--- a/reports/Debug-snowbowl-20251217/For The Day (Actual)_Payroll.xlsx
+++ b/reports/Debug-snowbowl-20251217/For The Day (Actual)_Payroll.xlsx
@@ -14,20 +14,95 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="982" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="989" uniqueCount="246">
   <si>
     <t>eecode</t>
   </si>
   <si>
+    <t>C346</t>
+  </si>
+  <si>
+    <t>F058</t>
+  </si>
+  <si>
+    <t>A280</t>
+  </si>
+  <si>
+    <t>A3MF</t>
+  </si>
+  <si>
+    <t>A2BY</t>
+  </si>
+  <si>
+    <t>A3P9</t>
+  </si>
+  <si>
+    <t>G693</t>
+  </si>
+  <si>
+    <t>H632</t>
+  </si>
+  <si>
+    <t>G891</t>
+  </si>
+  <si>
+    <t>H777</t>
+  </si>
+  <si>
+    <t>A0AF</t>
+  </si>
+  <si>
+    <t>A2C3</t>
+  </si>
+  <si>
+    <t>A3MT</t>
+  </si>
+  <si>
+    <t>A3NP</t>
+  </si>
+  <si>
+    <t>A3OD</t>
+  </si>
+  <si>
+    <t>A3OF</t>
+  </si>
+  <si>
+    <t>A3MQ</t>
+  </si>
+  <si>
+    <t>A4BY</t>
+  </si>
+  <si>
+    <t>B925</t>
+  </si>
+  <si>
+    <t>A3MC</t>
+  </si>
+  <si>
+    <t>A0BB</t>
+  </si>
+  <si>
+    <t>F627</t>
+  </si>
+  <si>
     <t>A337</t>
   </si>
   <si>
-    <t>A2BY</t>
+    <t>A2DQ</t>
+  </si>
+  <si>
+    <t>A2C5</t>
+  </si>
+  <si>
+    <t>A2C6</t>
   </si>
   <si>
     <t>G961</t>
   </si>
   <si>
+    <t>A1K3</t>
+  </si>
+  <si>
     <t>E483</t>
   </si>
   <si>
@@ -40,159 +115,84 @@
     <t>A749</t>
   </si>
   <si>
-    <t>A4BY</t>
-  </si>
-  <si>
-    <t>A3MQ</t>
-  </si>
-  <si>
-    <t>A3OF</t>
-  </si>
-  <si>
-    <t>A3OD</t>
-  </si>
-  <si>
-    <t>A3NP</t>
-  </si>
-  <si>
-    <t>A3MT</t>
-  </si>
-  <si>
-    <t>A2C3</t>
-  </si>
-  <si>
-    <t>A0AF</t>
-  </si>
-  <si>
-    <t>C346</t>
-  </si>
-  <si>
-    <t>B925</t>
-  </si>
-  <si>
-    <t>A3MC</t>
-  </si>
-  <si>
-    <t>A0BB</t>
-  </si>
-  <si>
-    <t>A3MF</t>
-  </si>
-  <si>
-    <t>A280</t>
-  </si>
-  <si>
-    <t>F058</t>
-  </si>
-  <si>
-    <t>A2C5</t>
+    <t>H352</t>
   </si>
   <si>
     <t>A2BR</t>
   </si>
   <si>
-    <t>A3P9</t>
-  </si>
-  <si>
-    <t>G693</t>
-  </si>
-  <si>
-    <t>H352</t>
-  </si>
-  <si>
-    <t>A1K3</t>
-  </si>
-  <si>
-    <t>G891</t>
-  </si>
-  <si>
-    <t>H777</t>
-  </si>
-  <si>
-    <t>H632</t>
-  </si>
-  <si>
-    <t>A2C6</t>
-  </si>
-  <si>
-    <t>A2DQ</t>
-  </si>
-  <si>
-    <t>F627</t>
-  </si>
-  <si>
     <t>E657</t>
   </si>
   <si>
     <t>A434</t>
   </si>
   <si>
+    <t>B221</t>
+  </si>
+  <si>
     <t>A3J5</t>
   </si>
   <si>
-    <t>B221</t>
-  </si>
-  <si>
     <t>A3I8</t>
   </si>
   <si>
+    <t>A3IP</t>
+  </si>
+  <si>
+    <t>A3IC</t>
+  </si>
+  <si>
+    <t>A0QH</t>
+  </si>
+  <si>
+    <t>A3LE</t>
+  </si>
+  <si>
+    <t>E530</t>
+  </si>
+  <si>
+    <t>J561</t>
+  </si>
+  <si>
     <t>A3IA</t>
   </si>
   <si>
     <t>A0QK</t>
   </si>
   <si>
-    <t>J561</t>
+    <t>A3J1</t>
+  </si>
+  <si>
+    <t>E568</t>
+  </si>
+  <si>
+    <t>A3IG</t>
   </si>
   <si>
     <t>A3WC</t>
   </si>
   <si>
-    <t>A3IP</t>
-  </si>
-  <si>
-    <t>A3IC</t>
-  </si>
-  <si>
-    <t>A3J1</t>
-  </si>
-  <si>
-    <t>E568</t>
-  </si>
-  <si>
-    <t>E530</t>
-  </si>
-  <si>
-    <t>A3LE</t>
-  </si>
-  <si>
-    <t>A3IG</t>
-  </si>
-  <si>
-    <t>A0QH</t>
+    <t>I806</t>
+  </si>
+  <si>
+    <t>A10D</t>
   </si>
   <si>
     <t>A2YJ</t>
   </si>
   <si>
-    <t>I806</t>
-  </si>
-  <si>
     <t>F703</t>
   </si>
   <si>
-    <t>A10D</t>
+    <t>C349</t>
+  </si>
+  <si>
+    <t>C215</t>
   </si>
   <si>
     <t>I305</t>
   </si>
   <si>
-    <t>C215</t>
-  </si>
-  <si>
-    <t>C349</t>
-  </si>
-  <si>
     <t>B567</t>
   </si>
   <si>
@@ -202,144 +202,147 @@
     <t>A235</t>
   </si>
   <si>
+    <t>G190</t>
+  </si>
+  <si>
     <t>A3HZ</t>
   </si>
   <si>
+    <t>G581</t>
+  </si>
+  <si>
+    <t>C644</t>
+  </si>
+  <si>
+    <t>E893</t>
+  </si>
+  <si>
+    <t>F013</t>
+  </si>
+  <si>
+    <t>G573</t>
+  </si>
+  <si>
+    <t>I588</t>
+  </si>
+  <si>
+    <t>A278</t>
+  </si>
+  <si>
     <t>H425</t>
   </si>
   <si>
+    <t>A400</t>
+  </si>
+  <si>
+    <t>D576</t>
+  </si>
+  <si>
     <t>H115</t>
   </si>
   <si>
-    <t>G573</t>
-  </si>
-  <si>
-    <t>C644</t>
-  </si>
-  <si>
-    <t>G581</t>
-  </si>
-  <si>
-    <t>E893</t>
-  </si>
-  <si>
-    <t>I588</t>
-  </si>
-  <si>
-    <t>A400</t>
-  </si>
-  <si>
-    <t>A278</t>
-  </si>
-  <si>
     <t>J289</t>
   </si>
   <si>
-    <t>F013</t>
-  </si>
-  <si>
-    <t>D576</t>
-  </si>
-  <si>
     <t>D619</t>
   </si>
   <si>
     <t>E660</t>
   </si>
   <si>
-    <t>G190</t>
+    <t>C991</t>
+  </si>
+  <si>
+    <t>A0QI</t>
+  </si>
+  <si>
+    <t>A4FM</t>
+  </si>
+  <si>
+    <t>A3RR</t>
+  </si>
+  <si>
+    <t>A2FB</t>
+  </si>
+  <si>
+    <t>A2FK</t>
+  </si>
+  <si>
+    <t>A0TR</t>
+  </si>
+  <si>
+    <t>A3X5</t>
+  </si>
+  <si>
+    <t>A3OG</t>
+  </si>
+  <si>
+    <t>A3RQ</t>
   </si>
   <si>
     <t>A2CR</t>
   </si>
   <si>
-    <t>A3OG</t>
+    <t>A842</t>
   </si>
   <si>
     <t>F510</t>
   </si>
   <si>
-    <t>A3RR</t>
-  </si>
-  <si>
-    <t>A3RQ</t>
-  </si>
-  <si>
-    <t>A3X5</t>
-  </si>
-  <si>
-    <t>A0TR</t>
-  </si>
-  <si>
-    <t>C991</t>
-  </si>
-  <si>
-    <t>A842</t>
-  </si>
-  <si>
     <t>H173</t>
   </si>
   <si>
-    <t>A0QI</t>
-  </si>
-  <si>
-    <t>A2FK</t>
-  </si>
-  <si>
-    <t>A2FB</t>
+    <t>G605</t>
+  </si>
+  <si>
+    <t>E190</t>
+  </si>
+  <si>
+    <t>A399</t>
   </si>
   <si>
     <t>A1PM</t>
   </si>
   <si>
-    <t>G605</t>
-  </si>
-  <si>
-    <t>A399</t>
-  </si>
-  <si>
-    <t>E190</t>
+    <t>A3RK</t>
+  </si>
+  <si>
+    <t>A44H</t>
+  </si>
+  <si>
+    <t>A3O7</t>
+  </si>
+  <si>
+    <t>H439</t>
   </si>
   <si>
     <t>A2IE</t>
   </si>
   <si>
+    <t>A3IY</t>
+  </si>
+  <si>
+    <t>A2BQ</t>
+  </si>
+  <si>
+    <t>A3O2</t>
+  </si>
+  <si>
+    <t>A3LK</t>
+  </si>
+  <si>
+    <t>A2JE</t>
+  </si>
+  <si>
+    <t>A2I3</t>
+  </si>
+  <si>
     <t>A0IQ</t>
   </si>
   <si>
-    <t>A2BQ</t>
-  </si>
-  <si>
-    <t>A2I3</t>
-  </si>
-  <si>
-    <t>A3O2</t>
-  </si>
-  <si>
-    <t>A3LK</t>
-  </si>
-  <si>
-    <t>A3RK</t>
-  </si>
-  <si>
-    <t>A44H</t>
-  </si>
-  <si>
-    <t>H439</t>
-  </si>
-  <si>
-    <t>A3O7</t>
-  </si>
-  <si>
-    <t>A3IY</t>
-  </si>
-  <si>
     <t>A0RX</t>
   </si>
   <si>
-    <t>A2JE</t>
-  </si>
-  <si>
     <t>F370</t>
   </si>
   <si>
@@ -352,99 +355,99 @@
     <t>A3KO</t>
   </si>
   <si>
+    <t>A0FY</t>
+  </si>
+  <si>
     <t>A3XF</t>
   </si>
   <si>
-    <t>A0FY</t>
-  </si>
-  <si>
     <t>A3KP</t>
   </si>
   <si>
+    <t>A3JL</t>
+  </si>
+  <si>
+    <t>A3YI</t>
+  </si>
+  <si>
+    <t>A0TT</t>
+  </si>
+  <si>
+    <t>A1MH</t>
+  </si>
+  <si>
+    <t>A2KH</t>
+  </si>
+  <si>
+    <t>A2ID</t>
+  </si>
+  <si>
+    <t>A3ZD</t>
+  </si>
+  <si>
+    <t>A3NK</t>
+  </si>
+  <si>
+    <t>A3TU</t>
+  </si>
+  <si>
+    <t>E478</t>
+  </si>
+  <si>
+    <t>A3KG</t>
+  </si>
+  <si>
     <t>A3JQ</t>
   </si>
   <si>
-    <t>A3ZD</t>
-  </si>
-  <si>
-    <t>E478</t>
-  </si>
-  <si>
-    <t>A3NK</t>
-  </si>
-  <si>
-    <t>A3TU</t>
-  </si>
-  <si>
     <t>E794</t>
   </si>
   <si>
-    <t>A2ID</t>
-  </si>
-  <si>
-    <t>A0TT</t>
-  </si>
-  <si>
-    <t>A1MH</t>
-  </si>
-  <si>
-    <t>A3KG</t>
-  </si>
-  <si>
-    <t>A3JL</t>
-  </si>
-  <si>
-    <t>A2KH</t>
-  </si>
-  <si>
-    <t>A3YI</t>
+    <t>A41H</t>
+  </si>
+  <si>
+    <t>A3ZB</t>
+  </si>
+  <si>
+    <t>A3TQ</t>
+  </si>
+  <si>
+    <t>A45O</t>
+  </si>
+  <si>
+    <t>A995</t>
+  </si>
+  <si>
+    <t>A3TV</t>
+  </si>
+  <si>
+    <t>A3J4</t>
+  </si>
+  <si>
+    <t>A0VA</t>
+  </si>
+  <si>
+    <t>A2K2</t>
+  </si>
+  <si>
+    <t>A3UE</t>
+  </si>
+  <si>
+    <t>A41E</t>
+  </si>
+  <si>
+    <t>C926</t>
+  </si>
+  <si>
+    <t>A3Z8</t>
   </si>
   <si>
     <t>A3I6</t>
   </si>
   <si>
-    <t>A0VA</t>
-  </si>
-  <si>
-    <t>A41E</t>
-  </si>
-  <si>
-    <t>A3UE</t>
-  </si>
-  <si>
-    <t>A2K2</t>
-  </si>
-  <si>
-    <t>C926</t>
-  </si>
-  <si>
-    <t>A45O</t>
-  </si>
-  <si>
-    <t>A995</t>
-  </si>
-  <si>
-    <t>A3TQ</t>
-  </si>
-  <si>
-    <t>A41H</t>
-  </si>
-  <si>
     <t>A3ZE</t>
   </si>
   <si>
-    <t>A3Z8</t>
-  </si>
-  <si>
-    <t>A3ZB</t>
-  </si>
-  <si>
-    <t>A3TV</t>
-  </si>
-  <si>
-    <t>A3J4</t>
-  </si>
-  <si>
     <t>A3Z9</t>
   </si>
   <si>
@@ -460,22 +463,28 @@
     <t>I017</t>
   </si>
   <si>
+    <t>A3HE</t>
+  </si>
+  <si>
     <t>A2HX</t>
   </si>
   <si>
     <t>E926</t>
   </si>
   <si>
-    <t>A3HE</t>
+    <t>A2GD</t>
+  </si>
+  <si>
+    <t>A3OP</t>
   </si>
   <si>
     <t>A194</t>
   </si>
   <si>
-    <t>A3OP</t>
-  </si>
-  <si>
-    <t>A2GD</t>
+    <t>G024</t>
+  </si>
+  <si>
+    <t>A3SU</t>
   </si>
   <si>
     <t>A4AF</t>
@@ -484,54 +493,48 @@
     <t>A0BO</t>
   </si>
   <si>
-    <t>A3SU</t>
-  </si>
-  <si>
-    <t>G024</t>
+    <t>A4AL</t>
   </si>
   <si>
     <t>A3SV</t>
   </si>
   <si>
-    <t>A4AL</t>
-  </si>
-  <si>
     <t>A2V1</t>
   </si>
   <si>
     <t>A0J5</t>
   </si>
   <si>
+    <t>A3PS</t>
+  </si>
+  <si>
     <t>A39M</t>
   </si>
   <si>
-    <t>A3PS</t>
+    <t>A0IJ</t>
+  </si>
+  <si>
+    <t>D754</t>
   </si>
   <si>
     <t>A3O6</t>
   </si>
   <si>
-    <t>A0IJ</t>
-  </si>
-  <si>
-    <t>D754</t>
-  </si>
-  <si>
     <t>A3TX</t>
   </si>
   <si>
+    <t>A3TW</t>
+  </si>
+  <si>
     <t>A2PQ</t>
   </si>
   <si>
-    <t>A3TW</t>
+    <t>J280</t>
   </si>
   <si>
     <t>A415</t>
   </si>
   <si>
-    <t>J280</t>
-  </si>
-  <si>
     <t>A393</t>
   </si>
   <si>
@@ -548,6 +551,9 @@
   </si>
   <si>
     <t>ID</t>
+  </si>
+  <si>
+    <t>IL</t>
   </si>
   <si>
     <t>HR</t>
@@ -1108,7 +1114,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J197"/>
+  <dimension ref="A1:J198"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.7109375" customWidth="1"/>
@@ -1127,31 +1133,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -1159,22 +1165,22 @@
         <v>1</v>
       </c>
       <c r="B2" s="2">
-        <v>46008.33333333334</v>
+        <v>46008.33283564815</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D2" s="2">
-        <v>46008.69444444445</v>
+        <v>46008.70064814815</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G2" s="2">
-        <v>18.6</v>
+        <v>19.6</v>
       </c>
       <c r="H2" s="2">
         <v>0</v>
@@ -1183,7 +1189,7 @@
         <v>0</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -1191,22 +1197,22 @@
         <v>2</v>
       </c>
       <c r="B3" s="2">
-        <v>46008.32557870371</v>
+        <v>46008.32430555556</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D3" s="2">
-        <v>46008.68519675926</v>
+        <v>46008.69541666667</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G3" s="2">
-        <v>18.6</v>
+        <v>20.7</v>
       </c>
       <c r="H3" s="2">
         <v>0</v>
@@ -1215,7 +1221,7 @@
         <v>0</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -1223,22 +1229,22 @@
         <v>3</v>
       </c>
       <c r="B4" s="2">
-        <v>46008.33234953704</v>
+        <v>46008.32291666666</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D4" s="2">
-        <v>46008.64033564815</v>
+        <v>46008.72232638889</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G4" s="2">
-        <v>19.6</v>
+        <v>23.35</v>
       </c>
       <c r="H4" s="2">
         <v>0</v>
@@ -1247,7 +1253,7 @@
         <v>0</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -1255,19 +1261,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="2">
-        <v>46008.32550925926</v>
+        <v>46008.32487268518</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D5" s="2">
-        <v>46008.375</v>
+        <v>46008.69575231482</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G5" s="2">
         <v>18.35</v>
@@ -1279,7 +1285,7 @@
         <v>0</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -1287,22 +1293,22 @@
         <v>5</v>
       </c>
       <c r="B6" s="2">
-        <v>46008.32969907407</v>
+        <v>46008.32557870371</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D6" s="2">
-        <v>46008.69554398148</v>
+        <v>46008.68519675926</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G6" s="2">
-        <v>19.6</v>
+        <v>18.6</v>
       </c>
       <c r="H6" s="2">
         <v>0</v>
@@ -1311,7 +1317,7 @@
         <v>0</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1319,22 +1325,22 @@
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>46008.33351851852</v>
+        <v>46008.3244212963</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D7" s="2">
-        <v>46008.70524305556</v>
+        <v>46008.68768518518</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G7" s="2">
-        <v>20.95</v>
+        <v>18.35</v>
       </c>
       <c r="H7" s="2">
         <v>0</v>
@@ -1343,7 +1349,7 @@
         <v>0</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1351,19 +1357,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="2">
-        <v>46008.32743055555</v>
+        <v>46008.32986111111</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D8" s="2">
-        <v>46008.68011574074</v>
+        <v>46008.68402777778</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G8" s="2">
         <v>18.35</v>
@@ -1375,7 +1381,7 @@
         <v>0</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1383,22 +1389,22 @@
         <v>8</v>
       </c>
       <c r="B9" s="2">
-        <v>46008.33189814815</v>
+        <v>46008.32291666666</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D9" s="2">
-        <v>46008.69172453704</v>
+        <v>46008.72673611111</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G9" s="2">
-        <v>18.35</v>
+        <v>26.8</v>
       </c>
       <c r="H9" s="2">
         <v>0</v>
@@ -1407,7 +1413,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -1415,22 +1421,22 @@
         <v>9</v>
       </c>
       <c r="B10" s="2">
-        <v>46008.32560185185</v>
+        <v>46008.33375</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D10" s="2">
-        <v>46008.68967592593</v>
+        <v>46008.70540509259</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G10" s="2">
-        <v>18.35</v>
+        <v>19.6</v>
       </c>
       <c r="H10" s="2">
         <v>0</v>
@@ -1439,7 +1445,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -1447,22 +1453,22 @@
         <v>10</v>
       </c>
       <c r="B11" s="2">
-        <v>46008.32673611111</v>
+        <v>46008.32438657407</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D11" s="2">
-        <v>46008.68945601852</v>
+        <v>46008.68748842592</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G11" s="2">
-        <v>18.35</v>
+        <v>20.7</v>
       </c>
       <c r="H11" s="2">
         <v>0</v>
@@ -1471,7 +1477,7 @@
         <v>0</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -1479,22 +1485,22 @@
         <v>11</v>
       </c>
       <c r="B12" s="2">
-        <v>46008.32545138889</v>
+        <v>46008.32313657407</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D12" s="2">
-        <v>46008.69276620371</v>
+        <v>46008.70289351852</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G12" s="2">
-        <v>19.25</v>
+        <v>18.7</v>
       </c>
       <c r="H12" s="2">
         <v>0</v>
@@ -1503,7 +1509,7 @@
         <v>0</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -1511,22 +1517,22 @@
         <v>12</v>
       </c>
       <c r="B13" s="2">
-        <v>46008.32380787037</v>
+        <v>46008.32291666666</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D13" s="2">
-        <v>46008.63894675926</v>
+        <v>46008.69649305556</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G13" s="2">
-        <v>18.35</v>
+        <v>19.25</v>
       </c>
       <c r="H13" s="2">
         <v>0</v>
@@ -1535,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -1546,16 +1552,16 @@
         <v>46008.3265625</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D14" s="2">
         <v>46008.69108796296</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G14" s="2">
         <v>18.35</v>
@@ -1567,7 +1573,7 @@
         <v>0</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -1575,22 +1581,22 @@
         <v>14</v>
       </c>
       <c r="B15" s="2">
-        <v>46008.32291666666</v>
+        <v>46008.32380787037</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D15" s="2">
-        <v>46008.69649305556</v>
+        <v>46008.63894675926</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G15" s="2">
-        <v>19.25</v>
+        <v>18.35</v>
       </c>
       <c r="H15" s="2">
         <v>0</v>
@@ -1599,7 +1605,7 @@
         <v>0</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -1607,22 +1613,22 @@
         <v>15</v>
       </c>
       <c r="B16" s="2">
-        <v>46008.32313657407</v>
+        <v>46008.32545138889</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D16" s="2">
-        <v>46008.70289351852</v>
+        <v>46008.69276620371</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G16" s="2">
-        <v>18.7</v>
+        <v>19.25</v>
       </c>
       <c r="H16" s="2">
         <v>0</v>
@@ -1631,7 +1637,7 @@
         <v>0</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -1639,22 +1645,22 @@
         <v>16</v>
       </c>
       <c r="B17" s="2">
-        <v>46008.33283564815</v>
+        <v>46008.32673611111</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D17" s="2">
-        <v>46008.70064814815</v>
+        <v>46008.68945601852</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G17" s="2">
-        <v>19.6</v>
+        <v>18.35</v>
       </c>
       <c r="H17" s="2">
         <v>0</v>
@@ -1663,7 +1669,7 @@
         <v>0</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -1671,22 +1677,22 @@
         <v>17</v>
       </c>
       <c r="B18" s="2">
-        <v>46008.32606481481</v>
+        <v>46008.32560185185</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D18" s="2">
-        <v>46008.70650462963</v>
+        <v>46008.68967592593</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G18" s="2">
-        <v>23.35</v>
+        <v>18.35</v>
       </c>
       <c r="H18" s="2">
         <v>0</v>
@@ -1695,7 +1701,7 @@
         <v>0</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -1703,19 +1709,19 @@
         <v>18</v>
       </c>
       <c r="B19" s="2">
-        <v>46008.33280092593</v>
+        <v>46008.33189814815</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D19" s="2">
-        <v>46008.68201388889</v>
+        <v>46008.69172453704</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G19" s="2">
         <v>18.35</v>
@@ -1727,7 +1733,7 @@
         <v>0</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -1735,22 +1741,22 @@
         <v>19</v>
       </c>
       <c r="B20" s="2">
-        <v>46008.33181712963</v>
+        <v>46008.32606481481</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D20" s="2">
-        <v>46008.69259259259</v>
+        <v>46008.70650462963</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G20" s="2">
-        <v>18.7</v>
+        <v>23.35</v>
       </c>
       <c r="H20" s="2">
         <v>0</v>
@@ -1759,7 +1765,7 @@
         <v>0</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -1767,19 +1773,19 @@
         <v>20</v>
       </c>
       <c r="B21" s="2">
-        <v>46008.32487268518</v>
+        <v>46008.33280092593</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D21" s="2">
-        <v>46008.69575231482</v>
+        <v>46008.68201388889</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G21" s="2">
         <v>18.35</v>
@@ -1791,7 +1797,7 @@
         <v>0</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -1799,22 +1805,22 @@
         <v>21</v>
       </c>
       <c r="B22" s="2">
-        <v>46008.32291666666</v>
+        <v>46008.33181712963</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D22" s="2">
-        <v>46008.72232638889</v>
+        <v>46008.69259259259</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G22" s="2">
-        <v>23.35</v>
+        <v>18.7</v>
       </c>
       <c r="H22" s="2">
         <v>0</v>
@@ -1823,7 +1829,7 @@
         <v>0</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -1831,22 +1837,22 @@
         <v>22</v>
       </c>
       <c r="B23" s="2">
-        <v>46008.32430555556</v>
+        <v>46008.32581018518</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D23" s="2">
-        <v>46008.69541666667</v>
+        <v>46008.7016087963</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G23" s="2">
-        <v>20.7</v>
+        <v>18.7</v>
       </c>
       <c r="H23" s="2">
         <v>0</v>
@@ -1855,7 +1861,7 @@
         <v>0</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -1863,19 +1869,19 @@
         <v>23</v>
       </c>
       <c r="B24" s="2">
-        <v>46008.32614583334</v>
+        <v>46008.33333333334</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D24" s="2">
-        <v>46008.63429398148</v>
+        <v>46008.69444444445</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G24" s="2">
         <v>18.6</v>
@@ -1887,7 +1893,7 @@
         <v>0</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -1895,19 +1901,19 @@
         <v>24</v>
       </c>
       <c r="B25" s="2">
-        <v>46008.33065972223</v>
+        <v>46008.32618055555</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D25" s="2">
-        <v>46008.70504629629</v>
+        <v>46008.64355324074</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G25" s="2">
         <v>18.6</v>
@@ -1919,7 +1925,7 @@
         <v>0</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -1927,22 +1933,22 @@
         <v>25</v>
       </c>
       <c r="B26" s="2">
-        <v>46008.3244212963</v>
+        <v>46008.32614583334</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D26" s="2">
-        <v>46008.68768518518</v>
+        <v>46008.63429398148</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G26" s="2">
-        <v>18.35</v>
+        <v>18.6</v>
       </c>
       <c r="H26" s="2">
         <v>0</v>
@@ -1951,7 +1957,7 @@
         <v>0</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -1959,22 +1965,22 @@
         <v>26</v>
       </c>
       <c r="B27" s="2">
-        <v>46008.32986111111</v>
+        <v>46008.32365740741</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D27" s="2">
-        <v>46008.68402777778</v>
+        <v>46008.68619212963</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G27" s="2">
-        <v>18.35</v>
+        <v>18.6</v>
       </c>
       <c r="H27" s="2">
         <v>0</v>
@@ -1983,7 +1989,7 @@
         <v>0</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -1991,22 +1997,22 @@
         <v>27</v>
       </c>
       <c r="B28" s="2">
-        <v>46008.32340277778</v>
+        <v>46008.33234953704</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D28" s="2">
-        <v>46008.68664351852</v>
+        <v>46008.64033564815</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G28" s="2">
-        <v>18.7</v>
+        <v>19.6</v>
       </c>
       <c r="H28" s="2">
         <v>0</v>
@@ -2015,7 +2021,7 @@
         <v>0</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -2026,16 +2032,16 @@
         <v>46008.32362268519</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D29" s="2">
         <v>46008.69126157407</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G29" s="2">
         <v>18.6</v>
@@ -2047,7 +2053,7 @@
         <v>0</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -2055,22 +2061,22 @@
         <v>29</v>
       </c>
       <c r="B30" s="2">
-        <v>46008.33375</v>
+        <v>46008.32550925926</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D30" s="2">
-        <v>46008.70540509259</v>
+        <v>46008.375</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G30" s="2">
-        <v>19.6</v>
+        <v>18.35</v>
       </c>
       <c r="H30" s="2">
         <v>0</v>
@@ -2079,7 +2085,7 @@
         <v>0</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -2087,22 +2093,22 @@
         <v>30</v>
       </c>
       <c r="B31" s="2">
-        <v>46008.32438657407</v>
+        <v>46008.32969907407</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D31" s="2">
-        <v>46008.68748842592</v>
+        <v>46008.69554398148</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G31" s="2">
-        <v>20.7</v>
+        <v>19.6</v>
       </c>
       <c r="H31" s="2">
         <v>0</v>
@@ -2111,7 +2117,7 @@
         <v>0</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -2119,22 +2125,22 @@
         <v>31</v>
       </c>
       <c r="B32" s="2">
-        <v>46008.32291666666</v>
+        <v>46008.33351851852</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D32" s="2">
-        <v>46008.72673611111</v>
+        <v>46008.70524305556</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G32" s="2">
-        <v>26.8</v>
+        <v>20.95</v>
       </c>
       <c r="H32" s="2">
         <v>0</v>
@@ -2143,7 +2149,7 @@
         <v>0</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="33" spans="1:10">
@@ -2151,22 +2157,22 @@
         <v>32</v>
       </c>
       <c r="B33" s="2">
-        <v>46008.32365740741</v>
+        <v>46008.32743055555</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D33" s="2">
-        <v>46008.68619212963</v>
+        <v>46008.68011574074</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G33" s="2">
-        <v>18.6</v>
+        <v>18.35</v>
       </c>
       <c r="H33" s="2">
         <v>0</v>
@@ -2175,7 +2181,7 @@
         <v>0</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="34" spans="1:10">
@@ -2183,22 +2189,22 @@
         <v>33</v>
       </c>
       <c r="B34" s="2">
-        <v>46008.32618055555</v>
+        <v>46008.32340277778</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D34" s="2">
-        <v>46008.64355324074</v>
+        <v>46008.68664351852</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G34" s="2">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="H34" s="2">
         <v>0</v>
@@ -2207,7 +2213,7 @@
         <v>0</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="35" spans="1:10">
@@ -2215,22 +2221,22 @@
         <v>34</v>
       </c>
       <c r="B35" s="2">
-        <v>46008.32581018518</v>
+        <v>46008.33065972223</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D35" s="2">
-        <v>46008.7016087963</v>
+        <v>46008.70504629629</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G35" s="2">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="H35" s="2">
         <v>0</v>
@@ -2239,7 +2245,7 @@
         <v>0</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="36" spans="1:10">
@@ -2250,16 +2256,16 @@
         <v>46008.28884259259</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D36" s="2">
         <v>46008.72241898148</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="G36" s="2">
         <v>45.68</v>
@@ -2271,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="37" spans="1:10">
@@ -2282,16 +2288,16 @@
         <v>46008.29103009259</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D37" s="2">
         <v>46008.72443287037</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="G37" s="2">
         <v>23.35</v>
@@ -2303,7 +2309,7 @@
         <v>0</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="38" spans="1:10">
@@ -2311,22 +2317,22 @@
         <v>37</v>
       </c>
       <c r="B38" s="2">
-        <v>46008.28938657408</v>
+        <v>46008.29186342593</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D38" s="2">
-        <v>46008.7019212963</v>
+        <v>46008.70943287037</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="G38" s="2">
-        <v>20.2</v>
+        <v>27</v>
       </c>
       <c r="H38" s="2">
         <v>0</v>
@@ -2335,7 +2341,7 @@
         <v>0</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="39" spans="1:10">
@@ -2343,22 +2349,22 @@
         <v>38</v>
       </c>
       <c r="B39" s="2">
-        <v>46008.29186342593</v>
+        <v>46008.28938657408</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D39" s="2">
-        <v>46008.70943287037</v>
+        <v>46008.7019212963</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="G39" s="2">
-        <v>27</v>
+        <v>20.2</v>
       </c>
       <c r="H39" s="2">
         <v>0</v>
@@ -2367,7 +2373,7 @@
         <v>0</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="40" spans="1:10">
@@ -2378,12 +2384,12 @@
         <v>46008.29003472222</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D40" s="2"/>
       <c r="E40" s="2"/>
       <c r="F40" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="G40" s="2">
         <v>22.4</v>
@@ -2395,7 +2401,7 @@
         <v>0</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="41" spans="1:10">
@@ -2403,22 +2409,22 @@
         <v>40</v>
       </c>
       <c r="B41" s="2">
-        <v>46008.10144675926</v>
+        <v>46008.06795138889</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D41" s="2">
-        <v>46008.49847222222</v>
+        <v>46008.51491898148</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="G41" s="2">
-        <v>20.2</v>
+        <v>23</v>
       </c>
       <c r="H41" s="2">
         <v>0</v>
@@ -2427,7 +2433,7 @@
         <v>0</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="42" spans="1:10">
@@ -2435,22 +2441,22 @@
         <v>41</v>
       </c>
       <c r="B42" s="2">
-        <v>46008.49791666667</v>
+        <v>46008.49631944444</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D42" s="2">
-        <v>46009.00070601852</v>
+        <v>46008.83351851852</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="G42" s="2">
-        <v>23</v>
+        <v>20.2</v>
       </c>
       <c r="H42" s="2">
         <v>0</v>
@@ -2459,7 +2465,7 @@
         <v>0</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="43" spans="1:10">
@@ -2467,22 +2473,22 @@
         <v>42</v>
       </c>
       <c r="B43" s="2">
-        <v>46008.49782407407</v>
+        <v>46008.51004629629</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D43" s="2">
-        <v>46009.00129629629</v>
+        <v>46008.83659722222</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="G43" s="2">
-        <v>22.4</v>
+        <v>23</v>
       </c>
       <c r="H43" s="2">
         <v>0</v>
@@ -2491,7 +2497,7 @@
         <v>0</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="44" spans="1:10">
@@ -2499,19 +2505,15 @@
         <v>43</v>
       </c>
       <c r="B44" s="2">
-        <v>46008.12863425926</v>
+        <v>46008.99462962963</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="D44" s="2">
-        <v>46008.50048611111</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>181</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="D44" s="2"/>
+      <c r="E44" s="2"/>
       <c r="F44" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="G44" s="2">
         <v>20.2</v>
@@ -2523,7 +2525,7 @@
         <v>0</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="45" spans="1:10">
@@ -2531,22 +2533,22 @@
         <v>44</v>
       </c>
       <c r="B45" s="2">
-        <v>46008.06795138889</v>
+        <v>46008.07349537037</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D45" s="2">
-        <v>46008.51491898148</v>
+        <v>46008.50157407407</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="G45" s="2">
-        <v>23</v>
+        <v>20.2</v>
       </c>
       <c r="H45" s="2">
         <v>0</v>
@@ -2555,27 +2557,23 @@
         <v>0</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="46" spans="1:10">
       <c r="A46" s="2" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B46" s="2">
-        <v>46008.4984837963</v>
+        <v>46008.99108796296</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="D46" s="2">
-        <v>46008.49856481481</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>181</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="D46" s="2"/>
+      <c r="E46" s="2"/>
       <c r="F46" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="G46" s="2">
         <v>20.2</v>
@@ -2587,7 +2585,7 @@
         <v>0</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="47" spans="1:10">
@@ -2595,22 +2593,22 @@
         <v>45</v>
       </c>
       <c r="B47" s="2">
-        <v>46008.49631944444</v>
+        <v>46008.49782407407</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D47" s="2">
-        <v>46008.83351851852</v>
+        <v>46009.00129629629</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="G47" s="2">
-        <v>20.2</v>
+        <v>22.4</v>
       </c>
       <c r="H47" s="2">
         <v>0</v>
@@ -2619,7 +2617,7 @@
         <v>0</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="48" spans="1:10">
@@ -2627,19 +2625,19 @@
         <v>46</v>
       </c>
       <c r="B48" s="2">
-        <v>46008.65560185185</v>
+        <v>46008.4984837963</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D48" s="2">
-        <v>46009.00068287037</v>
+        <v>46008.49856481481</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="G48" s="2">
         <v>20.2</v>
@@ -2651,7 +2649,7 @@
         <v>0</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="49" spans="1:10">
@@ -2659,22 +2657,22 @@
         <v>47</v>
       </c>
       <c r="B49" s="2">
-        <v>46008.29240740741</v>
+        <v>46008.49791666667</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D49" s="2">
-        <v>46008.72971064815</v>
+        <v>46009.00070601852</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="G49" s="2">
-        <v>30.75</v>
+        <v>23</v>
       </c>
       <c r="H49" s="2">
         <v>0</v>
@@ -2683,23 +2681,27 @@
         <v>0</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="50" spans="1:10">
       <c r="A50" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B50" s="2">
-        <v>46008.99108796296</v>
+        <v>46008.10144675926</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="D50" s="2"/>
-      <c r="E50" s="2"/>
+        <v>178</v>
+      </c>
+      <c r="D50" s="2">
+        <v>46008.49847222222</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>183</v>
+      </c>
       <c r="F50" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="G50" s="2">
         <v>20.2</v>
@@ -2711,7 +2713,7 @@
         <v>0</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="51" spans="1:10">
@@ -2719,19 +2721,19 @@
         <v>48</v>
       </c>
       <c r="B51" s="2">
-        <v>46008.07349537037</v>
+        <v>46008.65560185185</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D51" s="2">
-        <v>46008.50157407407</v>
+        <v>46009.00068287037</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="G51" s="2">
         <v>20.2</v>
@@ -2743,7 +2745,7 @@
         <v>0</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="52" spans="1:10">
@@ -2751,18 +2753,22 @@
         <v>49</v>
       </c>
       <c r="B52" s="2">
-        <v>46008.99462962963</v>
+        <v>46008.29240740741</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="D52" s="2"/>
-      <c r="E52" s="2"/>
+        <v>178</v>
+      </c>
+      <c r="D52" s="2">
+        <v>46008.72971064815</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>183</v>
+      </c>
       <c r="F52" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="G52" s="2">
-        <v>20.2</v>
+        <v>30.75</v>
       </c>
       <c r="H52" s="2">
         <v>0</v>
@@ -2771,7 +2777,7 @@
         <v>0</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="53" spans="1:10">
@@ -2782,16 +2788,16 @@
         <v>46008.00262731482</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D53" s="2">
         <v>46008.43054398148</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="G53" s="2">
         <v>20.2</v>
@@ -2803,7 +2809,7 @@
         <v>0</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="54" spans="1:10">
@@ -2811,22 +2817,22 @@
         <v>51</v>
       </c>
       <c r="B54" s="2">
-        <v>46008.51004629629</v>
+        <v>46008.12863425926</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D54" s="2">
-        <v>46008.83659722222</v>
+        <v>46008.50048611111</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="G54" s="2">
-        <v>23</v>
+        <v>20.2</v>
       </c>
       <c r="H54" s="2">
         <v>0</v>
@@ -2835,7 +2841,7 @@
         <v>0</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="55" spans="1:10">
@@ -2843,22 +2849,22 @@
         <v>52</v>
       </c>
       <c r="B55" s="2">
-        <v>46008.3234837963</v>
+        <v>46008.35998842592</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D55" s="2">
-        <v>46008.73959490741</v>
+        <v>46008.42685185185</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="G55" s="2">
-        <v>17.85</v>
+        <v>24</v>
       </c>
       <c r="H55" s="2">
         <v>0</v>
@@ -2867,27 +2873,27 @@
         <v>0</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="56" spans="1:10">
       <c r="A56" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B56" s="2">
         <v>46008.6916550926</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D56" s="2">
         <v>46009.0703125</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="G56" s="2">
         <v>24</v>
@@ -2899,7 +2905,7 @@
         <v>0</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="57" spans="1:10">
@@ -2907,22 +2913,22 @@
         <v>53</v>
       </c>
       <c r="B57" s="2">
-        <v>46008.35998842592</v>
+        <v>46008.31847222222</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D57" s="2">
-        <v>46008.42685185185</v>
+        <v>46008.73983796296</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="G57" s="2">
-        <v>24</v>
+        <v>18.6</v>
       </c>
       <c r="H57" s="2">
         <v>0</v>
@@ -2931,7 +2937,7 @@
         <v>0</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="58" spans="1:10">
@@ -2939,18 +2945,22 @@
         <v>54</v>
       </c>
       <c r="B58" s="2">
-        <v>46008.30304398148</v>
+        <v>46008.3234837963</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="D58" s="2"/>
-      <c r="E58" s="2"/>
+        <v>178</v>
+      </c>
+      <c r="D58" s="2">
+        <v>46008.73959490741</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>183</v>
+      </c>
       <c r="F58" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="G58" s="2">
-        <v>24</v>
+        <v>17.85</v>
       </c>
       <c r="H58" s="2">
         <v>0</v>
@@ -2959,7 +2969,7 @@
         <v>0</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="59" spans="1:10">
@@ -2967,22 +2977,18 @@
         <v>55</v>
       </c>
       <c r="B59" s="2">
-        <v>46008.31847222222</v>
+        <v>46008.30304398148</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="D59" s="2">
-        <v>46008.73983796296</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>181</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="D59" s="2"/>
+      <c r="E59" s="2"/>
       <c r="F59" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="G59" s="2">
-        <v>18.6</v>
+        <v>24</v>
       </c>
       <c r="H59" s="2">
         <v>0</v>
@@ -2991,7 +2997,7 @@
         <v>0</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="60" spans="1:10">
@@ -2999,18 +3005,22 @@
         <v>56</v>
       </c>
       <c r="B60" s="2">
-        <v>46008.08167824074</v>
+        <v>46008.69114583333</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="D60" s="2"/>
-      <c r="E60" s="2"/>
+        <v>178</v>
+      </c>
+      <c r="D60" s="2">
+        <v>46009.08342592593</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>183</v>
+      </c>
       <c r="F60" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="G60" s="2">
-        <v>20.7</v>
+        <v>29.25</v>
       </c>
       <c r="H60" s="2">
         <v>0</v>
@@ -3019,7 +3029,7 @@
         <v>0</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="61" spans="1:10">
@@ -3030,16 +3040,16 @@
         <v>46008.06891203704</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D61" s="2">
         <v>46008.39761574074</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="G61" s="2">
         <v>22.4</v>
@@ -3051,7 +3061,7 @@
         <v>0</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="62" spans="1:10">
@@ -3059,22 +3069,18 @@
         <v>58</v>
       </c>
       <c r="B62" s="2">
-        <v>46008.69114583333</v>
+        <v>46008.08167824074</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="D62" s="2">
-        <v>46009.08342592593</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>181</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="D62" s="2"/>
+      <c r="E62" s="2"/>
       <c r="F62" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="G62" s="2">
-        <v>29.25</v>
+        <v>20.7</v>
       </c>
       <c r="H62" s="2">
         <v>0</v>
@@ -3083,7 +3089,7 @@
         <v>0</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="63" spans="1:10">
@@ -3094,16 +3100,16 @@
         <v>46008.2818287037</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D63" s="2">
         <v>46008.50841435185</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="G63" s="2">
         <v>35.5</v>
@@ -3115,30 +3121,30 @@
         <v>0</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="64" spans="1:10">
       <c r="A64" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B64" s="2">
-        <v>46008.7293287037</v>
+        <v>46008.52883101852</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D64" s="2">
-        <v>46008.72991898148</v>
+        <v>46008.7253587963</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="G64" s="2">
-        <v>40.5</v>
+        <v>35.5</v>
       </c>
       <c r="H64" s="2">
         <v>0</v>
@@ -3147,30 +3153,30 @@
         <v>0</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="65" spans="1:10">
       <c r="A65" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B65" s="2">
-        <v>46008.52883101852</v>
+        <v>46008.7293287037</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D65" s="2">
-        <v>46008.7253587963</v>
+        <v>46008.72991898148</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="G65" s="2">
-        <v>35.5</v>
+        <v>40.5</v>
       </c>
       <c r="H65" s="2">
         <v>0</v>
@@ -3179,7 +3185,7 @@
         <v>0</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="66" spans="1:10">
@@ -3190,16 +3196,16 @@
         <v>46008.31883101852</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D66" s="2">
         <v>46008.72695601852</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="G66" s="2">
         <v>22.4</v>
@@ -3211,7 +3217,7 @@
         <v>0</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="67" spans="1:10">
@@ -3219,22 +3225,22 @@
         <v>62</v>
       </c>
       <c r="B67" s="2">
-        <v>46008.32776620371</v>
+        <v>46008.35416666666</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D67" s="2">
-        <v>46008.73819444444</v>
+        <v>46008.75209490741</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="G67" s="2">
-        <v>19.25</v>
+        <v>24.8</v>
       </c>
       <c r="H67" s="2">
         <v>0</v>
@@ -3243,7 +3249,7 @@
         <v>0</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="68" spans="1:10">
@@ -3251,22 +3257,22 @@
         <v>63</v>
       </c>
       <c r="B68" s="2">
-        <v>46008.32707175926</v>
+        <v>46008.32776620371</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D68" s="2">
-        <v>46008.75263888889</v>
+        <v>46008.73819444444</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="G68" s="2">
-        <v>20.95</v>
+        <v>19.25</v>
       </c>
       <c r="H68" s="2">
         <v>0</v>
@@ -3275,7 +3281,7 @@
         <v>0</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="69" spans="1:10">
@@ -3283,22 +3289,22 @@
         <v>64</v>
       </c>
       <c r="B69" s="2">
-        <v>46008.31787037037</v>
+        <v>46008.33200231481</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D69" s="2">
-        <v>46008.71130787037</v>
+        <v>46008.71427083333</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="G69" s="2">
-        <v>23.85</v>
+        <v>20.2</v>
       </c>
       <c r="H69" s="2">
         <v>0</v>
@@ -3307,7 +3313,7 @@
         <v>0</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="70" spans="1:10">
@@ -3315,22 +3321,22 @@
         <v>65</v>
       </c>
       <c r="B70" s="2">
-        <v>46008.31648148148</v>
+        <v>46008.32122685185</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D70" s="2">
-        <v>46008.75439814815</v>
+        <v>46008.32125</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="G70" s="2">
-        <v>24.45</v>
+        <v>23.35</v>
       </c>
       <c r="H70" s="2">
         <v>0</v>
@@ -3339,7 +3345,7 @@
         <v>0</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="71" spans="1:10">
@@ -3347,22 +3353,22 @@
         <v>66</v>
       </c>
       <c r="B71" s="2">
-        <v>46008.32122685185</v>
+        <v>46008.32806712963</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D71" s="2">
-        <v>46008.32125</v>
+        <v>46008.74947916667</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="G71" s="2">
-        <v>23.35</v>
+        <v>22.4</v>
       </c>
       <c r="H71" s="2">
         <v>0</v>
@@ -3371,7 +3377,7 @@
         <v>0</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="72" spans="1:10">
@@ -3379,22 +3385,22 @@
         <v>67</v>
       </c>
       <c r="B72" s="2">
-        <v>46008.33200231481</v>
+        <v>46008.33157407407</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D72" s="2">
-        <v>46008.71427083333</v>
+        <v>46008.71809027778</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="G72" s="2">
-        <v>20.2</v>
+        <v>22.4</v>
       </c>
       <c r="H72" s="2">
         <v>0</v>
@@ -3403,7 +3409,7 @@
         <v>0</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="73" spans="1:10">
@@ -3411,22 +3417,22 @@
         <v>68</v>
       </c>
       <c r="B73" s="2">
-        <v>46008.32806712963</v>
+        <v>46008.31648148148</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D73" s="2">
-        <v>46008.74947916667</v>
+        <v>46008.75439814815</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="G73" s="2">
-        <v>22.4</v>
+        <v>24.45</v>
       </c>
       <c r="H73" s="2">
         <v>0</v>
@@ -3435,7 +3441,7 @@
         <v>0</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="74" spans="1:10">
@@ -3446,16 +3452,16 @@
         <v>46008.32858796296</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D74" s="2">
         <v>46008.72153935185</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="G74" s="2">
         <v>20.7</v>
@@ -3467,7 +3473,7 @@
         <v>0</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="75" spans="1:10">
@@ -3475,22 +3481,22 @@
         <v>70</v>
       </c>
       <c r="B75" s="2">
-        <v>46008.32228009259</v>
+        <v>46008.32178240741</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D75" s="2">
-        <v>46008.74369212963</v>
+        <v>46008.63890046296</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="G75" s="2">
-        <v>23.35</v>
+        <v>20.95</v>
       </c>
       <c r="H75" s="2">
         <v>0</v>
@@ -3499,7 +3505,7 @@
         <v>0</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="76" spans="1:10">
@@ -3507,19 +3513,19 @@
         <v>71</v>
       </c>
       <c r="B76" s="2">
-        <v>46008.32178240741</v>
+        <v>46008.32707175926</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D76" s="2">
-        <v>46008.63890046296</v>
+        <v>46008.75263888889</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="G76" s="2">
         <v>20.95</v>
@@ -3531,7 +3537,7 @@
         <v>0</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="77" spans="1:10">
@@ -3539,22 +3545,22 @@
         <v>72</v>
       </c>
       <c r="B77" s="2">
-        <v>46008.31638888889</v>
+        <v>46008.32228009259</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D77" s="2">
-        <v>46008.71950231482</v>
+        <v>46008.74369212963</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="G77" s="2">
-        <v>19.6</v>
+        <v>23.35</v>
       </c>
       <c r="H77" s="2">
         <v>0</v>
@@ -3563,7 +3569,7 @@
         <v>0</v>
       </c>
       <c r="J77" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="78" spans="1:10">
@@ -3571,22 +3577,22 @@
         <v>73</v>
       </c>
       <c r="B78" s="2">
-        <v>46008.33157407407</v>
+        <v>46008.3278125</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D78" s="2">
-        <v>46008.71809027778</v>
+        <v>46008.75625</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="G78" s="2">
-        <v>22.4</v>
+        <v>23</v>
       </c>
       <c r="H78" s="2">
         <v>0</v>
@@ -3595,7 +3601,7 @@
         <v>0</v>
       </c>
       <c r="J78" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="79" spans="1:10">
@@ -3603,22 +3609,22 @@
         <v>74</v>
       </c>
       <c r="B79" s="2">
-        <v>46008.3278125</v>
+        <v>46008.31787037037</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D79" s="2">
-        <v>46008.75625</v>
+        <v>46008.71130787037</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="G79" s="2">
-        <v>23</v>
+        <v>23.85</v>
       </c>
       <c r="H79" s="2">
         <v>0</v>
@@ -3627,7 +3633,7 @@
         <v>0</v>
       </c>
       <c r="J79" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="80" spans="1:10">
@@ -3635,22 +3641,22 @@
         <v>75</v>
       </c>
       <c r="B80" s="2">
-        <v>46008.32195601852</v>
+        <v>46008.31638888889</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D80" s="2">
-        <v>46008.73618055556</v>
+        <v>46008.71950231482</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="G80" s="2">
-        <v>23</v>
+        <v>19.6</v>
       </c>
       <c r="H80" s="2">
         <v>0</v>
@@ -3659,7 +3665,7 @@
         <v>0</v>
       </c>
       <c r="J80" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="81" spans="1:10">
@@ -3667,22 +3673,22 @@
         <v>76</v>
       </c>
       <c r="B81" s="2">
-        <v>46008.33006944445</v>
+        <v>46008.32195601852</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D81" s="2">
-        <v>46008.75033564815</v>
+        <v>46008.73618055556</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="G81" s="2">
-        <v>20.95</v>
+        <v>23</v>
       </c>
       <c r="H81" s="2">
         <v>0</v>
@@ -3691,7 +3697,7 @@
         <v>0</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="82" spans="1:10">
@@ -3699,22 +3705,22 @@
         <v>77</v>
       </c>
       <c r="B82" s="2">
-        <v>46008.35416666666</v>
+        <v>46008.33006944445</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D82" s="2">
-        <v>46008.75209490741</v>
+        <v>46008.75033564815</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="G82" s="2">
-        <v>24.8</v>
+        <v>20.95</v>
       </c>
       <c r="H82" s="2">
         <v>0</v>
@@ -3723,7 +3729,7 @@
         <v>0</v>
       </c>
       <c r="J82" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="83" spans="1:10">
@@ -3731,19 +3737,19 @@
         <v>78</v>
       </c>
       <c r="B83" s="2">
-        <v>46008.41998842593</v>
+        <v>46008.32273148148</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D83" s="2">
-        <v>46008.69869212963</v>
+        <v>46008.70833333334</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="G83" s="2">
         <v>22.4</v>
@@ -3755,7 +3761,7 @@
         <v>0</v>
       </c>
       <c r="J83" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="84" spans="1:10">
@@ -3763,22 +3769,22 @@
         <v>79</v>
       </c>
       <c r="B84" s="2">
-        <v>46008.32165509259</v>
+        <v>46008.32090277778</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D84" s="2">
-        <v>46008.52068287037</v>
+        <v>46008.66881944444</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="G84" s="2">
-        <v>19.25</v>
+        <v>19.75</v>
       </c>
       <c r="H84" s="2">
         <v>0</v>
@@ -3787,7 +3793,7 @@
         <v>0</v>
       </c>
       <c r="J84" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="85" spans="1:10">
@@ -3795,23 +3801,21 @@
         <v>80</v>
       </c>
       <c r="B85" s="2">
-        <v>46008.62109953703</v>
+        <v>46008.61111111111</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D85" s="2">
-        <v>46008.68658564815</v>
+        <v>46008.68888888889</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="G85" s="2">
-        <v>22.75</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="G85" s="2"/>
       <c r="H85" s="2">
         <v>0</v>
       </c>
@@ -3819,30 +3823,30 @@
         <v>0</v>
       </c>
       <c r="J85" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="86" spans="1:10">
       <c r="A86" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B86" s="2">
-        <v>46008.31987268518</v>
+        <v>46008.32243055556</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D86" s="2">
-        <v>46008.57938657407</v>
+        <v>46008.62440972222</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="G86" s="2">
-        <v>22.75</v>
+        <v>19.25</v>
       </c>
       <c r="H86" s="2">
         <v>0</v>
@@ -3851,30 +3855,30 @@
         <v>0</v>
       </c>
       <c r="J86" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="87" spans="1:10">
       <c r="A87" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B87" s="2">
-        <v>46008.32243055556</v>
+        <v>46008.31601851852</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D87" s="2">
-        <v>46008.62440972222</v>
+        <v>46008.67222222222</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="G87" s="2">
-        <v>19.25</v>
+        <v>19.6</v>
       </c>
       <c r="H87" s="2">
         <v>0</v>
@@ -3883,30 +3887,30 @@
         <v>0</v>
       </c>
       <c r="J87" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="88" spans="1:10">
       <c r="A88" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B88" s="2">
-        <v>46008.32020833333</v>
+        <v>46008.3241550926</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D88" s="2">
-        <v>46008.61266203703</v>
+        <v>46008.69350694444</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="G88" s="2">
-        <v>19.25</v>
+        <v>19.6</v>
       </c>
       <c r="H88" s="2">
         <v>0</v>
@@ -3915,30 +3919,30 @@
         <v>0</v>
       </c>
       <c r="J88" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="89" spans="1:10">
       <c r="A89" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B89" s="2">
-        <v>46008.32103009259</v>
+        <v>46008.32349537037</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D89" s="2">
-        <v>46008.49600694444</v>
+        <v>46008.67393518519</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="G89" s="2">
-        <v>19.35</v>
+        <v>19.6</v>
       </c>
       <c r="H89" s="2">
         <v>0</v>
@@ -3947,30 +3951,30 @@
         <v>0</v>
       </c>
       <c r="J89" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="90" spans="1:10">
       <c r="A90" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B90" s="2">
-        <v>46008.32349537037</v>
+        <v>46008.32103009259</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D90" s="2">
-        <v>46008.67393518519</v>
+        <v>46008.49600694444</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="G90" s="2">
-        <v>19.6</v>
+        <v>19.35</v>
       </c>
       <c r="H90" s="2">
         <v>0</v>
@@ -3979,26 +3983,30 @@
         <v>0</v>
       </c>
       <c r="J90" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="91" spans="1:10">
       <c r="A91" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B91" s="2">
-        <v>46008.32273148148</v>
+        <v>46008.32165509259</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="D91" s="2"/>
-      <c r="E91" s="2"/>
+        <v>178</v>
+      </c>
+      <c r="D91" s="2">
+        <v>46008.52068287037</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>183</v>
+      </c>
       <c r="F91" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="G91" s="2">
-        <v>22.4</v>
+        <v>19.25</v>
       </c>
       <c r="H91" s="2">
         <v>0</v>
@@ -4007,30 +4015,30 @@
         <v>0</v>
       </c>
       <c r="J91" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="92" spans="1:10">
       <c r="A92" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B92" s="2">
-        <v>46008.32041666667</v>
+        <v>46008.32020833333</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D92" s="2">
-        <v>46008.49927083333</v>
+        <v>46008.61266203703</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="G92" s="2">
-        <v>22.4</v>
+        <v>19.25</v>
       </c>
       <c r="H92" s="2">
         <v>0</v>
@@ -4039,30 +4047,30 @@
         <v>0</v>
       </c>
       <c r="J92" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="93" spans="1:10">
       <c r="A93" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B93" s="2">
-        <v>46008.4034837963</v>
+        <v>46008.41998842593</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D93" s="2">
-        <v>46008.67138888889</v>
+        <v>46008.69869212963</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="G93" s="2">
-        <v>17.65</v>
+        <v>22.4</v>
       </c>
       <c r="H93" s="2">
         <v>0</v>
@@ -4071,30 +4079,30 @@
         <v>0</v>
       </c>
       <c r="J93" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="94" spans="1:10">
       <c r="A94" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B94" s="2">
-        <v>46008.32090277778</v>
+        <v>46008.32041666667</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D94" s="2">
-        <v>46008.66881944444</v>
+        <v>46008.49927083333</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="G94" s="2">
-        <v>19.75</v>
+        <v>22.4</v>
       </c>
       <c r="H94" s="2">
         <v>0</v>
@@ -4103,30 +4111,30 @@
         <v>0</v>
       </c>
       <c r="J94" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="95" spans="1:10">
       <c r="A95" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B95" s="2">
-        <v>46008.3241550926</v>
+        <v>46008.62109953703</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D95" s="2">
-        <v>46008.69350694444</v>
+        <v>46008.68658564815</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="G95" s="2">
-        <v>19.6</v>
+        <v>22.75</v>
       </c>
       <c r="H95" s="2">
         <v>0</v>
@@ -4135,30 +4143,30 @@
         <v>0</v>
       </c>
       <c r="J95" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="96" spans="1:10">
       <c r="A96" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B96" s="2">
-        <v>46008.31601851852</v>
+        <v>46008.4034837963</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D96" s="2">
-        <v>46008.67222222222</v>
+        <v>46008.67138888889</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="G96" s="2">
-        <v>19.6</v>
+        <v>17.65</v>
       </c>
       <c r="H96" s="2">
         <v>0</v>
@@ -4167,30 +4175,30 @@
         <v>0</v>
       </c>
       <c r="J96" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="97" spans="1:10">
       <c r="A97" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B97" s="2">
-        <v>46008.33380787037</v>
+        <v>46008.31987268518</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D97" s="2">
-        <v>46008.68732638889</v>
+        <v>46008.57938657407</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G97" s="2">
-        <v>22.4</v>
+        <v>22.75</v>
       </c>
       <c r="H97" s="2">
         <v>0</v>
@@ -4199,7 +4207,7 @@
         <v>0</v>
       </c>
       <c r="J97" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="98" spans="1:10">
@@ -4210,16 +4218,16 @@
         <v>46008.32261574074</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D98" s="2">
         <v>46008.69291666667</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G98" s="2">
         <v>25.7</v>
@@ -4231,7 +4239,7 @@
         <v>0</v>
       </c>
       <c r="J98" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="99" spans="1:10">
@@ -4239,22 +4247,22 @@
         <v>93</v>
       </c>
       <c r="B99" s="2">
-        <v>46008.32594907407</v>
+        <v>46008.32351851852</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D99" s="2">
-        <v>46008.65208333333</v>
+        <v>46008.69104166667</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G99" s="2">
-        <v>23.35</v>
+        <v>23</v>
       </c>
       <c r="H99" s="2">
         <v>0</v>
@@ -4263,7 +4271,7 @@
         <v>0</v>
       </c>
       <c r="J99" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="100" spans="1:10">
@@ -4271,22 +4279,22 @@
         <v>94</v>
       </c>
       <c r="B100" s="2">
-        <v>46008.32351851852</v>
+        <v>46008.32594907407</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D100" s="2">
-        <v>46008.69104166667</v>
+        <v>46008.65208333333</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G100" s="2">
-        <v>23</v>
+        <v>23.35</v>
       </c>
       <c r="H100" s="2">
         <v>0</v>
@@ -4295,7 +4303,7 @@
         <v>0</v>
       </c>
       <c r="J100" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="101" spans="1:10">
@@ -4303,22 +4311,22 @@
         <v>95</v>
       </c>
       <c r="B101" s="2">
-        <v>46008.71534722222</v>
+        <v>46008.33380787037</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D101" s="2">
-        <v>46008.7244212963</v>
+        <v>46008.68732638889</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G101" s="2">
-        <v>18.6</v>
+        <v>22.4</v>
       </c>
       <c r="H101" s="2">
         <v>0</v>
@@ -4327,7 +4335,7 @@
         <v>0</v>
       </c>
       <c r="J101" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="102" spans="1:10">
@@ -4335,22 +4343,22 @@
         <v>96</v>
       </c>
       <c r="B102" s="2">
-        <v>46008.32204861111</v>
+        <v>46008.60657407407</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D102" s="2">
-        <v>46008.75659722222</v>
+        <v>46008.72299768519</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="G102" s="2">
-        <v>18.7</v>
+        <v>18.35</v>
       </c>
       <c r="H102" s="2">
         <v>0</v>
@@ -4359,7 +4367,7 @@
         <v>0</v>
       </c>
       <c r="J102" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="103" spans="1:10">
@@ -4367,22 +4375,22 @@
         <v>97</v>
       </c>
       <c r="B103" s="2">
-        <v>46008.32700231481</v>
+        <v>46008.3163425926</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D103" s="2">
-        <v>46008.75539351852</v>
+        <v>46008.46460648148</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="G103" s="2">
-        <v>22.4</v>
+        <v>18.35</v>
       </c>
       <c r="H103" s="2">
         <v>0</v>
@@ -4391,7 +4399,7 @@
         <v>0</v>
       </c>
       <c r="J103" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="104" spans="1:10">
@@ -4399,22 +4407,22 @@
         <v>98</v>
       </c>
       <c r="B104" s="2">
-        <v>46008.32693287037</v>
+        <v>46008.32166666666</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D104" s="2">
-        <v>46008.75811342592</v>
+        <v>46008.53768518518</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="G104" s="2">
-        <v>19.25</v>
+        <v>18.35</v>
       </c>
       <c r="H104" s="2">
         <v>0</v>
@@ -4423,27 +4431,27 @@
         <v>0</v>
       </c>
       <c r="J104" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="105" spans="1:10">
       <c r="A105" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B105" s="2">
-        <v>46008.58664351852</v>
+        <v>46008.56383101852</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D105" s="2">
-        <v>46008.72578703704</v>
+        <v>46008.72267361111</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="G105" s="2">
         <v>18.35</v>
@@ -4455,30 +4463,30 @@
         <v>0</v>
       </c>
       <c r="J105" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="106" spans="1:10">
       <c r="A106" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B106" s="2">
-        <v>46008.62387731481</v>
+        <v>46008.32508101852</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D106" s="2">
-        <v>46008.72387731481</v>
+        <v>46008.72265046297</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="G106" s="2">
-        <v>18.35</v>
+        <v>19.75</v>
       </c>
       <c r="H106" s="2">
         <v>0</v>
@@ -4487,27 +4495,27 @@
         <v>0</v>
       </c>
       <c r="J106" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="107" spans="1:10">
       <c r="A107" s="2" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="B107" s="2">
         <v>46008.32131944445</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D107" s="2">
         <v>46008.52903935185</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="G107" s="2">
         <v>18.6</v>
@@ -4519,30 +4527,30 @@
         <v>0</v>
       </c>
       <c r="J107" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="108" spans="1:10">
       <c r="A108" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B108" s="2">
-        <v>46008.31614583333</v>
+        <v>46008.71534722222</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D108" s="2">
-        <v>46008.5660300926</v>
+        <v>46008.7244212963</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="G108" s="2">
-        <v>18.35</v>
+        <v>18.6</v>
       </c>
       <c r="H108" s="2">
         <v>0</v>
@@ -4551,27 +4559,27 @@
         <v>0</v>
       </c>
       <c r="J108" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="109" spans="1:10">
       <c r="A109" s="2" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="B109" s="2">
         <v>46008.32050925926</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D109" s="2">
         <v>46008.58869212963</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="G109" s="2">
         <v>18.35</v>
@@ -4583,27 +4591,27 @@
         <v>0</v>
       </c>
       <c r="J109" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="110" spans="1:10">
       <c r="A110" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B110" s="2">
-        <v>46008.53298611111</v>
+        <v>46008.53646990741</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D110" s="2">
-        <v>46008.72300925926</v>
+        <v>46008.72309027778</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="G110" s="2">
         <v>18.35</v>
@@ -4615,7 +4623,7 @@
         <v>0</v>
       </c>
       <c r="J110" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="111" spans="1:10">
@@ -4623,22 +4631,22 @@
         <v>102</v>
       </c>
       <c r="B111" s="2">
-        <v>46008.3163425926</v>
+        <v>46008.32700231481</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D111" s="2">
-        <v>46008.46460648148</v>
+        <v>46008.75539351852</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="G111" s="2">
-        <v>18.35</v>
+        <v>22.4</v>
       </c>
       <c r="H111" s="2">
         <v>0</v>
@@ -4647,7 +4655,7 @@
         <v>0</v>
       </c>
       <c r="J111" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="112" spans="1:10">
@@ -4655,22 +4663,22 @@
         <v>103</v>
       </c>
       <c r="B112" s="2">
-        <v>46008.32508101852</v>
+        <v>46008.31614583333</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D112" s="2">
-        <v>46008.72265046297</v>
+        <v>46008.5660300926</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="G112" s="2">
-        <v>19.75</v>
+        <v>18.35</v>
       </c>
       <c r="H112" s="2">
         <v>0</v>
@@ -4679,7 +4687,7 @@
         <v>0</v>
       </c>
       <c r="J112" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="113" spans="1:10">
@@ -4687,19 +4695,19 @@
         <v>104</v>
       </c>
       <c r="B113" s="2">
-        <v>46008.56383101852</v>
+        <v>46008.32394675926</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D113" s="2">
-        <v>46008.72267361111</v>
+        <v>46008.6040625</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="G113" s="2">
         <v>18.35</v>
@@ -4711,30 +4719,30 @@
         <v>0</v>
       </c>
       <c r="J113" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="114" spans="1:10">
       <c r="A114" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B114" s="2">
-        <v>46008.32166666666</v>
+        <v>46008.67943287037</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D114" s="2">
-        <v>46008.53768518518</v>
+        <v>46008.75774305555</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="G114" s="2">
-        <v>18.35</v>
+        <v>18.6</v>
       </c>
       <c r="H114" s="2">
         <v>0</v>
@@ -4743,30 +4751,30 @@
         <v>0</v>
       </c>
       <c r="J114" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="115" spans="1:10">
       <c r="A115" s="2" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="B115" s="2">
-        <v>46008.32394675926</v>
+        <v>46008.32693287037</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D115" s="2">
-        <v>46008.6040625</v>
+        <v>46008.75811342592</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="G115" s="2">
-        <v>18.35</v>
+        <v>19.25</v>
       </c>
       <c r="H115" s="2">
         <v>0</v>
@@ -4775,30 +4783,30 @@
         <v>0</v>
       </c>
       <c r="J115" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="116" spans="1:10">
       <c r="A116" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B116" s="2">
-        <v>46008.32136574074</v>
+        <v>46008.32204861111</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D116" s="2">
-        <v>46008.52903935185</v>
+        <v>46008.75659722222</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="G116" s="2">
-        <v>18.35</v>
+        <v>18.7</v>
       </c>
       <c r="H116" s="2">
         <v>0</v>
@@ -4807,30 +4815,30 @@
         <v>0</v>
       </c>
       <c r="J116" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="117" spans="1:10">
       <c r="A117" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B117" s="2">
-        <v>46008.32291666666</v>
+        <v>46008.32136574074</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D117" s="2">
-        <v>46008.72313657407</v>
+        <v>46008.52903935185</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="G117" s="2">
-        <v>18.7</v>
+        <v>18.35</v>
       </c>
       <c r="H117" s="2">
         <v>0</v>
@@ -4839,27 +4847,27 @@
         <v>0</v>
       </c>
       <c r="J117" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="118" spans="1:10">
       <c r="A118" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B118" s="2">
-        <v>46008.60657407407</v>
+        <v>46008.58664351852</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D118" s="2">
-        <v>46008.72299768519</v>
+        <v>46008.72578703704</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="G118" s="2">
         <v>18.35</v>
@@ -4871,30 +4879,30 @@
         <v>0</v>
       </c>
       <c r="J118" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="119" spans="1:10">
       <c r="A119" s="2" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="B119" s="2">
-        <v>46008.67943287037</v>
+        <v>46008.53298611111</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D119" s="2">
-        <v>46008.75774305555</v>
+        <v>46008.72300925926</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="G119" s="2">
-        <v>18.6</v>
+        <v>18.35</v>
       </c>
       <c r="H119" s="2">
         <v>0</v>
@@ -4903,30 +4911,30 @@
         <v>0</v>
       </c>
       <c r="J119" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="120" spans="1:10">
       <c r="A120" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B120" s="2">
-        <v>46008.53646990741</v>
+        <v>46008.32291666666</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D120" s="2">
-        <v>46008.72309027778</v>
+        <v>46008.72313657407</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="G120" s="2">
-        <v>18.35</v>
+        <v>18.7</v>
       </c>
       <c r="H120" s="2">
         <v>0</v>
@@ -4935,30 +4943,30 @@
         <v>0</v>
       </c>
       <c r="J120" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="121" spans="1:10">
       <c r="A121" s="2" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B121" s="2">
-        <v>46008.33344907407</v>
+        <v>46008.62387731481</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D121" s="2">
-        <v>46008.68002314815</v>
+        <v>46008.72387731481</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G121" s="2">
-        <v>19.75</v>
+        <v>18.35</v>
       </c>
       <c r="H121" s="2">
         <v>0</v>
@@ -4967,30 +4975,30 @@
         <v>0</v>
       </c>
       <c r="J121" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="122" spans="1:10">
       <c r="A122" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B122" s="2">
-        <v>46008.33045138889</v>
+        <v>46008.33344907407</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D122" s="2">
-        <v>46008.67932870371</v>
+        <v>46008.68002314815</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="G122" s="2">
-        <v>18.6</v>
+        <v>19.75</v>
       </c>
       <c r="H122" s="2">
         <v>0</v>
@@ -4999,30 +5007,30 @@
         <v>0</v>
       </c>
       <c r="J122" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="123" spans="1:10">
       <c r="A123" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B123" s="2">
-        <v>46008.3244212963</v>
+        <v>46008.33045138889</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D123" s="2">
-        <v>46008.75369212963</v>
+        <v>46008.67932870371</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G123" s="2">
-        <v>18.35</v>
+        <v>18.6</v>
       </c>
       <c r="H123" s="2">
         <v>0</v>
@@ -5031,7 +5039,7 @@
         <v>0</v>
       </c>
       <c r="J123" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="124" spans="1:10">
@@ -5039,22 +5047,22 @@
         <v>110</v>
       </c>
       <c r="B124" s="2">
-        <v>46008.33390046296</v>
+        <v>46008.3244212963</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D124" s="2">
-        <v>46008.53298611111</v>
+        <v>46008.75369212963</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G124" s="2">
-        <v>23</v>
+        <v>18.35</v>
       </c>
       <c r="H124" s="2">
         <v>0</v>
@@ -5063,27 +5071,27 @@
         <v>0</v>
       </c>
       <c r="J124" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="125" spans="1:10">
       <c r="A125" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B125" s="2">
         <v>46008.55153935185</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D125" s="2">
         <v>46008.7553125</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="G125" s="2">
         <v>23</v>
@@ -5095,7 +5103,7 @@
         <v>0</v>
       </c>
       <c r="J125" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="126" spans="1:10">
@@ -5103,22 +5111,22 @@
         <v>111</v>
       </c>
       <c r="B126" s="2">
-        <v>46008.70833333334</v>
+        <v>46008.33390046296</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D126" s="2">
-        <v>46008.75884259259</v>
+        <v>46008.53298611111</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="G126" s="2">
-        <v>18.35</v>
+        <v>23</v>
       </c>
       <c r="H126" s="2">
         <v>0</v>
@@ -5127,7 +5135,7 @@
         <v>0</v>
       </c>
       <c r="J126" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="127" spans="1:10">
@@ -5135,19 +5143,19 @@
         <v>112</v>
       </c>
       <c r="B127" s="2">
-        <v>46008.71449074074</v>
+        <v>46008.70833333334</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D127" s="2">
-        <v>46008.75619212963</v>
+        <v>46008.75884259259</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="G127" s="2">
         <v>18.35</v>
@@ -5159,7 +5167,7 @@
         <v>0</v>
       </c>
       <c r="J127" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="128" spans="1:10">
@@ -5170,16 +5178,16 @@
         <v>46008.33290509259</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D128" s="2">
         <v>46008.75527777777</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="G128" s="2">
         <v>18.6</v>
@@ -5191,7 +5199,7 @@
         <v>0</v>
       </c>
       <c r="J128" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="129" spans="1:10">
@@ -5199,19 +5207,19 @@
         <v>114</v>
       </c>
       <c r="B129" s="2">
-        <v>46008.37541666667</v>
+        <v>46008.71449074074</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D129" s="2">
-        <v>46008.77966435185</v>
+        <v>46008.75619212963</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G129" s="2">
         <v>18.35</v>
@@ -5223,7 +5231,7 @@
         <v>0</v>
       </c>
       <c r="J129" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="130" spans="1:10">
@@ -5231,22 +5239,22 @@
         <v>115</v>
       </c>
       <c r="B130" s="2">
-        <v>46008.26869212963</v>
+        <v>46008.37541666667</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D130" s="2">
-        <v>46008.5490625</v>
+        <v>46008.77966435185</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G130" s="2">
-        <v>22.4</v>
+        <v>18.35</v>
       </c>
       <c r="H130" s="2">
         <v>0</v>
@@ -5255,7 +5263,7 @@
         <v>0</v>
       </c>
       <c r="J130" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="131" spans="1:10">
@@ -5263,31 +5271,31 @@
         <v>116</v>
       </c>
       <c r="B131" s="2">
-        <v>46008.35864583333</v>
+        <v>46008.33333333334</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="D131" s="2">
-        <v>46008.70237268518</v>
+        <v>46008.33333333334</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="G131" s="2">
         <v>18.35</v>
       </c>
       <c r="H131" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I131" s="2">
         <v>0</v>
       </c>
       <c r="J131" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="132" spans="1:10">
@@ -5295,19 +5303,19 @@
         <v>117</v>
       </c>
       <c r="B132" s="2">
-        <v>46008.33428240741</v>
+        <v>46008.36841435185</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D132" s="2">
-        <v>46008.70704861111</v>
+        <v>46008.75363425926</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="G132" s="2">
         <v>18.35</v>
@@ -5319,62 +5327,62 @@
         <v>0</v>
       </c>
       <c r="J132" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="133" spans="1:10">
       <c r="A133" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B133" s="2">
-        <v>46008</v>
+        <v>46008.330625</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>178</v>
       </c>
       <c r="D133" s="2">
-        <v>46008</v>
+        <v>46008.58432870371</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="G133" s="2">
-        <v>18.35</v>
+        <v>18.7</v>
       </c>
       <c r="H133" s="2">
         <v>0</v>
       </c>
       <c r="I133" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J133" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="134" spans="1:10">
       <c r="A134" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B134" s="2">
-        <v>46008.38309027778</v>
+        <v>46008.375</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D134" s="2">
-        <v>46008.67697916667</v>
+        <v>46008.68541666667</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="G134" s="2">
-        <v>18.35</v>
+        <v>17.4</v>
       </c>
       <c r="H134" s="2">
         <v>0</v>
@@ -5383,27 +5391,27 @@
         <v>0</v>
       </c>
       <c r="J134" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="135" spans="1:10">
       <c r="A135" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B135" s="2">
-        <v>46008.34931712963</v>
+        <v>46008.37400462963</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D135" s="2">
-        <v>46008.70387731482</v>
+        <v>46008.68203703704</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="G135" s="2">
         <v>18.35</v>
@@ -5415,30 +5423,30 @@
         <v>0</v>
       </c>
       <c r="J135" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="136" spans="1:10">
       <c r="A136" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B136" s="2">
-        <v>46008.3317824074</v>
+        <v>46008.37298611111</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D136" s="2">
-        <v>46008.70861111111</v>
+        <v>46008.67597222222</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="G136" s="2">
-        <v>22.4</v>
+        <v>18.6</v>
       </c>
       <c r="H136" s="2">
         <v>0</v>
@@ -5447,30 +5455,30 @@
         <v>0</v>
       </c>
       <c r="J136" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="137" spans="1:10">
       <c r="A137" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B137" s="2">
-        <v>46008.37298611111</v>
+        <v>46008.35864583333</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D137" s="2">
-        <v>46008.67597222222</v>
+        <v>46008.70237268518</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="G137" s="2">
-        <v>18.6</v>
+        <v>18.35</v>
       </c>
       <c r="H137" s="2">
         <v>0</v>
@@ -5479,30 +5487,30 @@
         <v>0</v>
       </c>
       <c r="J137" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="138" spans="1:10">
       <c r="A138" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B138" s="2">
-        <v>46008.330625</v>
+        <v>46008.38309027778</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D138" s="2">
-        <v>46008.58432870371</v>
+        <v>46008.67697916667</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="G138" s="2">
-        <v>18.7</v>
+        <v>18.35</v>
       </c>
       <c r="H138" s="2">
         <v>0</v>
@@ -5511,30 +5519,30 @@
         <v>0</v>
       </c>
       <c r="J138" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="139" spans="1:10">
       <c r="A139" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B139" s="2">
-        <v>46008.375</v>
+        <v>46008.34931712963</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D139" s="2">
-        <v>46008.68541666667</v>
+        <v>46008.70387731482</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="G139" s="2">
-        <v>17.4</v>
+        <v>18.35</v>
       </c>
       <c r="H139" s="2">
         <v>0</v>
@@ -5543,27 +5551,27 @@
         <v>0</v>
       </c>
       <c r="J139" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="140" spans="1:10">
       <c r="A140" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B140" s="2">
-        <v>46008.45318287037</v>
+        <v>46008.33428240741</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D140" s="2">
-        <v>46008.69195601852</v>
+        <v>46008.70704861111</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="G140" s="2">
         <v>18.35</v>
@@ -5575,7 +5583,7 @@
         <v>0</v>
       </c>
       <c r="J140" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="141" spans="1:10">
@@ -5583,31 +5591,31 @@
         <v>125</v>
       </c>
       <c r="B141" s="2">
-        <v>46008.33333333334</v>
+        <v>46008</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D141" s="2">
-        <v>46008.33333333334</v>
+        <v>46008</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="G141" s="2">
         <v>18.35</v>
       </c>
       <c r="H141" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I141" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J141" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="142" spans="1:10">
@@ -5615,19 +5623,19 @@
         <v>126</v>
       </c>
       <c r="B142" s="2">
-        <v>46008.37400462963</v>
+        <v>46008.45318287037</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D142" s="2">
-        <v>46008.68203703704</v>
+        <v>46008.69195601852</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="G142" s="2">
         <v>18.35</v>
@@ -5639,7 +5647,7 @@
         <v>0</v>
       </c>
       <c r="J142" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="143" spans="1:10">
@@ -5647,22 +5655,22 @@
         <v>127</v>
       </c>
       <c r="B143" s="2">
-        <v>46008.36841435185</v>
+        <v>46008.26869212963</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D143" s="2">
-        <v>46008.75363425926</v>
+        <v>46008.5490625</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="G143" s="2">
-        <v>18.35</v>
+        <v>22.4</v>
       </c>
       <c r="H143" s="2">
         <v>0</v>
@@ -5671,7 +5679,7 @@
         <v>0</v>
       </c>
       <c r="J143" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="144" spans="1:10">
@@ -5679,22 +5687,22 @@
         <v>128</v>
       </c>
       <c r="B144" s="2">
-        <v>46008.30707175926</v>
+        <v>46008.3317824074</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D144" s="2">
-        <v>46008.6840162037</v>
+        <v>46008.70861111111</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G144" s="2">
-        <v>18.35</v>
+        <v>22.4</v>
       </c>
       <c r="H144" s="2">
         <v>0</v>
@@ -5703,7 +5711,7 @@
         <v>0</v>
       </c>
       <c r="J144" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="145" spans="1:10">
@@ -5711,22 +5719,22 @@
         <v>129</v>
       </c>
       <c r="B145" s="2">
-        <v>46008.2924537037</v>
+        <v>46008.45677083333</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D145" s="2">
-        <v>46008.75108796296</v>
+        <v>46008.73013888889</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="G145" s="2">
-        <v>21.8</v>
+        <v>18.35</v>
       </c>
       <c r="H145" s="2">
         <v>0</v>
@@ -5735,7 +5743,7 @@
         <v>0</v>
       </c>
       <c r="J145" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="146" spans="1:10">
@@ -5743,19 +5751,19 @@
         <v>130</v>
       </c>
       <c r="B146" s="2">
-        <v>46008.3041087963</v>
+        <v>46008.30898148148</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D146" s="2">
-        <v>46008.62412037037</v>
+        <v>46008.46837962963</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="G146" s="2">
         <v>18.35</v>
@@ -5767,7 +5775,7 @@
         <v>0</v>
       </c>
       <c r="J146" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="147" spans="1:10">
@@ -5775,31 +5783,31 @@
         <v>131</v>
       </c>
       <c r="B147" s="2">
-        <v>46008.45787037037</v>
+        <v>46008.33333333334</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="D147" s="2">
-        <v>46008.68711805555</v>
+        <v>46008.33333333334</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="G147" s="2">
         <v>18.35</v>
       </c>
       <c r="H147" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I147" s="2">
         <v>0</v>
       </c>
       <c r="J147" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="148" spans="1:10">
@@ -5807,54 +5815,54 @@
         <v>132</v>
       </c>
       <c r="B148" s="2">
-        <v>46008.33333333334</v>
+        <v>46008.37238425926</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>178</v>
       </c>
       <c r="D148" s="2">
-        <v>46008.33333333334</v>
+        <v>46008.65017361111</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="G148" s="2">
-        <v>18.6</v>
+        <v>18.35</v>
       </c>
       <c r="H148" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I148" s="2">
         <v>0</v>
       </c>
       <c r="J148" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="149" spans="1:10">
       <c r="A149" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B149" s="2">
-        <v>46008.30685185185</v>
+        <v>46008.53782407408</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D149" s="2">
-        <v>46008.68783564815</v>
+        <v>46008.6237962963</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="G149" s="2">
-        <v>19.65</v>
+        <v>18.35</v>
       </c>
       <c r="H149" s="2">
         <v>0</v>
@@ -5863,27 +5871,27 @@
         <v>0</v>
       </c>
       <c r="J149" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="150" spans="1:10">
       <c r="A150" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B150" s="2">
-        <v>46008.37238425926</v>
+        <v>46008.34783564815</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D150" s="2">
-        <v>46008.65017361111</v>
+        <v>46008.40863425926</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="G150" s="2">
         <v>18.35</v>
@@ -5895,27 +5903,27 @@
         <v>0</v>
       </c>
       <c r="J150" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="151" spans="1:10">
       <c r="A151" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B151" s="2">
-        <v>46008.41196759259</v>
+        <v>46008.37054398148</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D151" s="2">
-        <v>46008.75497685185</v>
+        <v>46008.65266203704</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="G151" s="2">
         <v>18.35</v>
@@ -5927,7 +5935,7 @@
         <v>0</v>
       </c>
       <c r="J151" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="152" spans="1:10">
@@ -5935,19 +5943,19 @@
         <v>135</v>
       </c>
       <c r="B152" s="2">
-        <v>46008.34783564815</v>
+        <v>46008.45280092592</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D152" s="2">
-        <v>46008.40863425926</v>
+        <v>46008.69300925926</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="G152" s="2">
         <v>18.35</v>
@@ -5959,7 +5967,7 @@
         <v>0</v>
       </c>
       <c r="J152" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="153" spans="1:10">
@@ -5967,51 +5975,51 @@
         <v>136</v>
       </c>
       <c r="B153" s="2">
-        <v>46008.33333333334</v>
+        <v>46008.2924537037</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>178</v>
       </c>
       <c r="D153" s="2">
-        <v>46008.33333333334</v>
+        <v>46008.75108796296</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="G153" s="2">
-        <v>18.35</v>
+        <v>21.8</v>
       </c>
       <c r="H153" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I153" s="2">
         <v>0</v>
       </c>
       <c r="J153" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="154" spans="1:10">
       <c r="A154" s="2" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B154" s="2">
-        <v>46008.45677083333</v>
+        <v>46008.41196759259</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D154" s="2">
-        <v>46008.73013888889</v>
+        <v>46008.75497685185</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="G154" s="2">
         <v>18.35</v>
@@ -6023,59 +6031,59 @@
         <v>0</v>
       </c>
       <c r="J154" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="155" spans="1:10">
       <c r="A155" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B155" s="2">
-        <v>46008.31267361111</v>
+        <v>46008.33333333334</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="D155" s="2">
-        <v>46008.6346875</v>
+        <v>46008.33333333334</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="G155" s="2">
-        <v>18.35</v>
+        <v>18.6</v>
       </c>
       <c r="H155" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I155" s="2">
         <v>0</v>
       </c>
       <c r="J155" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="156" spans="1:10">
       <c r="A156" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B156" s="2">
-        <v>46008.45525462963</v>
+        <v>46008.45787037037</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D156" s="2">
-        <v>46008.69054398148</v>
+        <v>46008.68711805555</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="G156" s="2">
         <v>18.35</v>
@@ -6087,27 +6095,27 @@
         <v>0</v>
       </c>
       <c r="J156" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="157" spans="1:10">
       <c r="A157" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B157" s="2">
-        <v>46008.53782407408</v>
+        <v>46008.3041087963</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D157" s="2">
-        <v>46008.6237962963</v>
+        <v>46008.62412037037</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="G157" s="2">
         <v>18.35</v>
@@ -6119,7 +6127,7 @@
         <v>0</v>
       </c>
       <c r="J157" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="158" spans="1:10">
@@ -6127,22 +6135,22 @@
         <v>140</v>
       </c>
       <c r="B158" s="2">
-        <v>46008.30898148148</v>
+        <v>46008.30685185185</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D158" s="2">
-        <v>46008.46837962963</v>
+        <v>46008.68783564815</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="G158" s="2">
-        <v>18.35</v>
+        <v>19.65</v>
       </c>
       <c r="H158" s="2">
         <v>0</v>
@@ -6151,7 +6159,7 @@
         <v>0</v>
       </c>
       <c r="J158" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="159" spans="1:10">
@@ -6159,19 +6167,19 @@
         <v>141</v>
       </c>
       <c r="B159" s="2">
-        <v>46008.37054398148</v>
+        <v>46008.45525462963</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D159" s="2">
-        <v>46008.65266203704</v>
+        <v>46008.69054398148</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="G159" s="2">
         <v>18.35</v>
@@ -6183,7 +6191,7 @@
         <v>0</v>
       </c>
       <c r="J159" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="160" spans="1:10">
@@ -6191,19 +6199,19 @@
         <v>142</v>
       </c>
       <c r="B160" s="2">
-        <v>46008.45280092592</v>
+        <v>46008.30707175926</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D160" s="2">
-        <v>46008.69300925926</v>
+        <v>46008.6840162037</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="G160" s="2">
         <v>18.35</v>
@@ -6215,7 +6223,7 @@
         <v>0</v>
       </c>
       <c r="J160" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="161" spans="1:10">
@@ -6223,19 +6231,19 @@
         <v>143</v>
       </c>
       <c r="B161" s="2">
-        <v>46008.45158564814</v>
+        <v>46008.31267361111</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D161" s="2">
-        <v>46008.69189814815</v>
+        <v>46008.6346875</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="G161" s="2">
         <v>18.35</v>
@@ -6247,7 +6255,7 @@
         <v>0</v>
       </c>
       <c r="J161" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="162" spans="1:10">
@@ -6255,22 +6263,22 @@
         <v>144</v>
       </c>
       <c r="B162" s="2">
-        <v>46008.57627314814</v>
+        <v>46008.45158564814</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D162" s="2">
-        <v>46008.89563657407</v>
+        <v>46008.69189814815</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G162" s="2">
-        <v>19.25</v>
+        <v>18.35</v>
       </c>
       <c r="H162" s="2">
         <v>0</v>
@@ -6279,7 +6287,7 @@
         <v>0</v>
       </c>
       <c r="J162" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="163" spans="1:10">
@@ -6287,19 +6295,19 @@
         <v>145</v>
       </c>
       <c r="B163" s="2">
-        <v>46008.56996527778</v>
+        <v>46008.57627314814</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D163" s="2">
-        <v>46008.91245370371</v>
+        <v>46008.89563657407</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="G163" s="2">
         <v>19.25</v>
@@ -6311,27 +6319,27 @@
         <v>0</v>
       </c>
       <c r="J163" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="164" spans="1:10">
       <c r="A164" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B164" s="2">
         <v>46008</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D164" s="2">
         <v>46008</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="G164" s="2">
         <v>19.25</v>
@@ -6343,7 +6351,7 @@
         <v>21</v>
       </c>
       <c r="J164" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="165" spans="1:10">
@@ -6351,22 +6359,22 @@
         <v>146</v>
       </c>
       <c r="B165" s="2">
-        <v>46008.36943287037</v>
+        <v>46008.56996527778</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D165" s="2">
-        <v>46008.68327546296</v>
+        <v>46008.91245370371</v>
       </c>
       <c r="E165" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G165" s="2">
-        <v>18.7</v>
+        <v>19.25</v>
       </c>
       <c r="H165" s="2">
         <v>0</v>
@@ -6375,7 +6383,7 @@
         <v>0</v>
       </c>
       <c r="J165" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="166" spans="1:10">
@@ -6383,22 +6391,22 @@
         <v>147</v>
       </c>
       <c r="B166" s="2">
-        <v>46008.35621527778</v>
+        <v>46008.36943287037</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D166" s="2">
-        <v>46008.68711805555</v>
+        <v>46008.68327546296</v>
       </c>
       <c r="E166" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="G166" s="2">
-        <v>25.7</v>
+        <v>18.7</v>
       </c>
       <c r="H166" s="2">
         <v>0</v>
@@ -6407,7 +6415,7 @@
         <v>0</v>
       </c>
       <c r="J166" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="167" spans="1:10">
@@ -6415,22 +6423,22 @@
         <v>148</v>
       </c>
       <c r="B167" s="2">
-        <v>46008.27208333334</v>
+        <v>46008.35621527778</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D167" s="2">
-        <v>46008.59503472222</v>
+        <v>46008.68711805555</v>
       </c>
       <c r="E167" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G167" s="2">
-        <v>17.85</v>
+        <v>25.7</v>
       </c>
       <c r="H167" s="2">
         <v>0</v>
@@ -6439,7 +6447,7 @@
         <v>0</v>
       </c>
       <c r="J167" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="168" spans="1:10">
@@ -6447,18 +6455,22 @@
         <v>149</v>
       </c>
       <c r="B168" s="2">
-        <v>46008.93788194445</v>
+        <v>46008.62002314815</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="D168" s="2"/>
-      <c r="E168" s="2"/>
+        <v>178</v>
+      </c>
+      <c r="D168" s="2">
+        <v>46008.91891203704</v>
+      </c>
+      <c r="E168" s="2" t="s">
+        <v>183</v>
+      </c>
       <c r="F168" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="G168" s="2">
-        <v>20.7</v>
+        <v>18.35</v>
       </c>
       <c r="H168" s="2">
         <v>0</v>
@@ -6467,7 +6479,7 @@
         <v>0</v>
       </c>
       <c r="J168" s="2" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="169" spans="1:10">
@@ -6475,22 +6487,22 @@
         <v>150</v>
       </c>
       <c r="B169" s="2">
-        <v>46008.62002314815</v>
+        <v>46008.27208333334</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D169" s="2">
-        <v>46008.91891203704</v>
+        <v>46008.59503472222</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="G169" s="2">
-        <v>18.35</v>
+        <v>17.85</v>
       </c>
       <c r="H169" s="2">
         <v>0</v>
@@ -6499,7 +6511,7 @@
         <v>0</v>
       </c>
       <c r="J169" s="2" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="170" spans="1:10">
@@ -6507,22 +6519,18 @@
         <v>151</v>
       </c>
       <c r="B170" s="2">
-        <v>46008.38293981482</v>
+        <v>46008.93788194445</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="D170" s="2">
-        <v>46008.85240740741</v>
-      </c>
-      <c r="E170" s="2" t="s">
-        <v>181</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="D170" s="2"/>
+      <c r="E170" s="2"/>
       <c r="F170" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G170" s="2">
-        <v>23</v>
+        <v>20.7</v>
       </c>
       <c r="H170" s="2">
         <v>0</v>
@@ -6531,7 +6539,7 @@
         <v>0</v>
       </c>
       <c r="J170" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="171" spans="1:10">
@@ -6539,22 +6547,22 @@
         <v>152</v>
       </c>
       <c r="B171" s="2">
-        <v>46008.40925925926</v>
+        <v>46008.37502314815</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D171" s="2">
-        <v>46008.66957175926</v>
+        <v>46008.66898148148</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="G171" s="2">
-        <v>20.2</v>
+        <v>19.65</v>
       </c>
       <c r="H171" s="2">
         <v>0</v>
@@ -6563,7 +6571,7 @@
         <v>0</v>
       </c>
       <c r="J171" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="172" spans="1:10">
@@ -6571,22 +6579,22 @@
         <v>153</v>
       </c>
       <c r="B172" s="2">
-        <v>46008.37502314815</v>
+        <v>46008.40925925926</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D172" s="2">
-        <v>46008.66898148148</v>
+        <v>46008.66957175926</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="G172" s="2">
-        <v>19.65</v>
+        <v>20.2</v>
       </c>
       <c r="H172" s="2">
         <v>0</v>
@@ -6595,7 +6603,7 @@
         <v>0</v>
       </c>
       <c r="J172" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="173" spans="1:10">
@@ -6603,22 +6611,22 @@
         <v>154</v>
       </c>
       <c r="B173" s="2">
-        <v>46008.33858796296</v>
+        <v>46008.38293981482</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D173" s="2">
-        <v>46008.47296296297</v>
+        <v>46008.85240740741</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="G173" s="2">
-        <v>19.25</v>
+        <v>23</v>
       </c>
       <c r="H173" s="2">
         <v>0</v>
@@ -6627,7 +6635,7 @@
         <v>0</v>
       </c>
       <c r="J173" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="174" spans="1:10">
@@ -6635,19 +6643,19 @@
         <v>155</v>
       </c>
       <c r="B174" s="2">
-        <v>46008.32636574074</v>
+        <v>46008.33918981482</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D174" s="2">
-        <v>46008.71285879629</v>
+        <v>46008.50122685185</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G174" s="2">
         <v>19.75</v>
@@ -6659,7 +6667,7 @@
         <v>0</v>
       </c>
       <c r="J174" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="175" spans="1:10">
@@ -6670,16 +6678,16 @@
         <v>46008.31644675926</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D175" s="2">
         <v>46008.48304398148</v>
       </c>
       <c r="E175" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G175" s="2">
         <v>19.25</v>
@@ -6691,7 +6699,7 @@
         <v>0</v>
       </c>
       <c r="J175" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="176" spans="1:10">
@@ -6699,22 +6707,22 @@
         <v>157</v>
       </c>
       <c r="B176" s="2">
-        <v>46008.33918981482</v>
+        <v>46008.33858796296</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D176" s="2">
-        <v>46008.50122685185</v>
+        <v>46008.47296296297</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G176" s="2">
-        <v>19.75</v>
+        <v>19.25</v>
       </c>
       <c r="H176" s="2">
         <v>0</v>
@@ -6723,7 +6731,7 @@
         <v>0</v>
       </c>
       <c r="J176" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="177" spans="1:10">
@@ -6731,22 +6739,22 @@
         <v>158</v>
       </c>
       <c r="B177" s="2">
-        <v>46008.31043981481</v>
+        <v>46008.32636574074</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D177" s="2">
-        <v>46008.47129629629</v>
+        <v>46008.71285879629</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G177" s="2">
-        <v>19.25</v>
+        <v>19.75</v>
       </c>
       <c r="H177" s="2">
         <v>0</v>
@@ -6755,7 +6763,7 @@
         <v>0</v>
       </c>
       <c r="J177" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="178" spans="1:10">
@@ -6766,16 +6774,16 @@
         <v>46008.32416666667</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D178" s="2">
         <v>46008.62644675926</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G178" s="2">
         <v>19.25</v>
@@ -6787,7 +6795,7 @@
         <v>0</v>
       </c>
       <c r="J178" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="179" spans="1:10">
@@ -6795,22 +6803,22 @@
         <v>160</v>
       </c>
       <c r="B179" s="2">
-        <v>46008.30429398148</v>
+        <v>46008.31043981481</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D179" s="2">
-        <v>46008.78543981481</v>
+        <v>46008.47129629629</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G179" s="2">
-        <v>22.4</v>
+        <v>19.25</v>
       </c>
       <c r="H179" s="2">
         <v>0</v>
@@ -6819,7 +6827,7 @@
         <v>0</v>
       </c>
       <c r="J179" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="180" spans="1:10">
@@ -6827,22 +6835,22 @@
         <v>161</v>
       </c>
       <c r="B180" s="2">
-        <v>46008.68947916666</v>
+        <v>46008.30429398148</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D180" s="2">
-        <v>46008.94432870371</v>
+        <v>46008.78543981481</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G180" s="2">
-        <v>19.65</v>
+        <v>22.4</v>
       </c>
       <c r="H180" s="2">
         <v>0</v>
@@ -6851,30 +6859,30 @@
         <v>0</v>
       </c>
       <c r="J180" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="181" spans="1:10">
       <c r="A181" s="2" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B181" s="2">
-        <v>46008.3325462963</v>
+        <v>46008.6847337963</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D181" s="2">
-        <v>46008.55449074074</v>
+        <v>46008.94347222222</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="G181" s="2">
-        <v>21.2</v>
+        <v>19.65</v>
       </c>
       <c r="H181" s="2">
         <v>0</v>
@@ -6883,7 +6891,7 @@
         <v>0</v>
       </c>
       <c r="J181" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="182" spans="1:10">
@@ -6891,18 +6899,22 @@
         <v>162</v>
       </c>
       <c r="B182" s="2">
-        <v>46008.57696759259</v>
+        <v>46008.68947916666</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="D182" s="2"/>
-      <c r="E182" s="2"/>
+        <v>178</v>
+      </c>
+      <c r="D182" s="2">
+        <v>46008.94432870371</v>
+      </c>
+      <c r="E182" s="2" t="s">
+        <v>183</v>
+      </c>
       <c r="F182" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="G182" s="2">
-        <v>21.2</v>
+        <v>19.65</v>
       </c>
       <c r="H182" s="2">
         <v>0</v>
@@ -6911,7 +6923,7 @@
         <v>0</v>
       </c>
       <c r="J182" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="183" spans="1:10">
@@ -6919,19 +6931,19 @@
         <v>163</v>
       </c>
       <c r="B183" s="2">
-        <v>46008.37226851852</v>
+        <v>46008.61809027778</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D183" s="2">
-        <v>46008.59844907407</v>
+        <v>46008.68962962963</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="G183" s="2">
         <v>20.7</v>
@@ -6943,7 +6955,7 @@
         <v>0</v>
       </c>
       <c r="J183" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="184" spans="1:10">
@@ -6951,19 +6963,19 @@
         <v>163</v>
       </c>
       <c r="B184" s="2">
-        <v>46008.61809027778</v>
+        <v>46008.37226851852</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D184" s="2">
-        <v>46008.68962962963</v>
+        <v>46008.59844907407</v>
       </c>
       <c r="E184" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="G184" s="2">
         <v>20.7</v>
@@ -6975,30 +6987,30 @@
         <v>0</v>
       </c>
       <c r="J184" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="185" spans="1:10">
       <c r="A185" s="2" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="B185" s="2">
-        <v>46008.6847337963</v>
+        <v>46008.57696759259</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D185" s="2">
-        <v>46008.94347222222</v>
+        <v>46009.32939814815</v>
       </c>
       <c r="E185" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="G185" s="2">
-        <v>19.65</v>
+        <v>21.2</v>
       </c>
       <c r="H185" s="2">
         <v>0</v>
@@ -7007,7 +7019,7 @@
         <v>0</v>
       </c>
       <c r="J185" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="186" spans="1:10">
@@ -7015,22 +7027,22 @@
         <v>164</v>
       </c>
       <c r="B186" s="2">
-        <v>46008.31932870371</v>
+        <v>46008.3325462963</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D186" s="2">
-        <v>46008.69688657407</v>
+        <v>46008.55449074074</v>
       </c>
       <c r="E186" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F186" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G186" s="2">
-        <v>26.5</v>
+        <v>21.2</v>
       </c>
       <c r="H186" s="2">
         <v>0</v>
@@ -7039,7 +7051,7 @@
         <v>0</v>
       </c>
       <c r="J186" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="187" spans="1:10">
@@ -7050,16 +7062,16 @@
         <v>46008.45568287037</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D187" s="2">
         <v>46008.83043981482</v>
       </c>
       <c r="E187" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F187" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="G187" s="2">
         <v>26.45</v>
@@ -7071,7 +7083,7 @@
         <v>0</v>
       </c>
       <c r="J187" s="2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="188" spans="1:10">
@@ -7082,16 +7094,16 @@
         <v>46008.31364583333</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D188" s="2">
         <v>46008.60549768519</v>
       </c>
       <c r="E188" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F188" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="G188" s="2">
         <v>22.75</v>
@@ -7103,7 +7115,7 @@
         <v>0</v>
       </c>
       <c r="J188" s="2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="189" spans="1:10">
@@ -7111,22 +7123,22 @@
         <v>167</v>
       </c>
       <c r="B189" s="2">
-        <v>46008.31380787037</v>
+        <v>46008.31932870371</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D189" s="2">
-        <v>46008.57020833333</v>
+        <v>46008.69688657407</v>
       </c>
       <c r="E189" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F189" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G189" s="2">
-        <v>30.78</v>
+        <v>26.5</v>
       </c>
       <c r="H189" s="2">
         <v>0</v>
@@ -7135,30 +7147,30 @@
         <v>0</v>
       </c>
       <c r="J189" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="190" spans="1:10">
       <c r="A190" s="2" t="s">
-        <v>60</v>
+        <v>168</v>
       </c>
       <c r="B190" s="2">
-        <v>46008.28983796296</v>
+        <v>46008.31380787037</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D190" s="2">
-        <v>46008.51706018519</v>
+        <v>46008.57020833333</v>
       </c>
       <c r="E190" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F190" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G190" s="2">
-        <v>40.5</v>
+        <v>30.78</v>
       </c>
       <c r="H190" s="2">
         <v>0</v>
@@ -7167,30 +7179,30 @@
         <v>0</v>
       </c>
       <c r="J190" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="191" spans="1:10">
       <c r="A191" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B191" s="2">
-        <v>46008.33887731482</v>
+        <v>46008.32768518518</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D191" s="2">
-        <v>46008.72604166667</v>
+        <v>46008.71399305556</v>
       </c>
       <c r="E191" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F191" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G191" s="2">
-        <v>31.64</v>
+        <v>30.78</v>
       </c>
       <c r="H191" s="2">
         <v>0</v>
@@ -7199,30 +7211,30 @@
         <v>0</v>
       </c>
       <c r="J191" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="192" spans="1:10">
       <c r="A192" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B192" s="2">
-        <v>46008.32768518518</v>
+        <v>46008.33887731482</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D192" s="2">
-        <v>46008.71399305556</v>
+        <v>46008.72604166667</v>
       </c>
       <c r="E192" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F192" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G192" s="2">
-        <v>30.78</v>
+        <v>31.64</v>
       </c>
       <c r="H192" s="2">
         <v>0</v>
@@ -7231,30 +7243,30 @@
         <v>0</v>
       </c>
       <c r="J192" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="193" spans="1:10">
       <c r="A193" s="2" t="s">
-        <v>170</v>
+        <v>60</v>
       </c>
       <c r="B193" s="2">
-        <v>46008.38196759259</v>
+        <v>46008.28983796296</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D193" s="2">
-        <v>46008.71839120371</v>
+        <v>46008.51706018519</v>
       </c>
       <c r="E193" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F193" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G193" s="2">
-        <v>23</v>
+        <v>40.5</v>
       </c>
       <c r="H193" s="2">
         <v>0</v>
@@ -7263,7 +7275,7 @@
         <v>0</v>
       </c>
       <c r="J193" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="194" spans="1:10">
@@ -7274,16 +7286,16 @@
         <v>46008.35969907408</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D194" s="2">
         <v>46008.70510416666</v>
       </c>
       <c r="E194" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F194" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="G194" s="2">
         <v>23</v>
@@ -7295,7 +7307,7 @@
         <v>0</v>
       </c>
       <c r="J194" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="195" spans="1:10">
@@ -7303,22 +7315,22 @@
         <v>172</v>
       </c>
       <c r="B195" s="2">
-        <v>46008.34535879629</v>
+        <v>46008.38196759259</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D195" s="2">
-        <v>46008.48449074074</v>
+        <v>46008.71839120371</v>
       </c>
       <c r="E195" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F195" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G195" s="2">
-        <v>26.75</v>
+        <v>23</v>
       </c>
       <c r="H195" s="2">
         <v>0</v>
@@ -7327,7 +7339,7 @@
         <v>0</v>
       </c>
       <c r="J195" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="196" spans="1:10">
@@ -7335,22 +7347,22 @@
         <v>173</v>
       </c>
       <c r="B196" s="2">
-        <v>46008.30726851852</v>
+        <v>46008.34535879629</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D196" s="2">
-        <v>46008.70521990741</v>
+        <v>46008.48449074074</v>
       </c>
       <c r="E196" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F196" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G196" s="2">
-        <v>21.4</v>
+        <v>26.75</v>
       </c>
       <c r="H196" s="2">
         <v>0</v>
@@ -7359,7 +7371,7 @@
         <v>0</v>
       </c>
       <c r="J196" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="197" spans="1:10">
@@ -7367,31 +7379,63 @@
         <v>174</v>
       </c>
       <c r="B197" s="2">
+        <v>46008.30726851852</v>
+      </c>
+      <c r="C197" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="D197" s="2">
+        <v>46008.70521990741</v>
+      </c>
+      <c r="E197" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="F197" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="G197" s="2">
+        <v>21.4</v>
+      </c>
+      <c r="H197" s="2">
+        <v>0</v>
+      </c>
+      <c r="I197" s="2">
+        <v>0</v>
+      </c>
+      <c r="J197" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="198" spans="1:10">
+      <c r="A198" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B198" s="2">
         <v>46008.33710648148</v>
       </c>
-      <c r="C197" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="D197" s="2">
+      <c r="C198" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="D198" s="2">
         <v>46008.67365740741</v>
       </c>
-      <c r="E197" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="F197" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="G197" s="2">
+      <c r="E198" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="F198" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="G198" s="2">
         <v>20.2</v>
       </c>
-      <c r="H197" s="2">
-        <v>0</v>
-      </c>
-      <c r="I197" s="2">
-        <v>0</v>
-      </c>
-      <c r="J197" s="2" t="s">
-        <v>178</v>
+      <c r="H198" s="2">
+        <v>0</v>
+      </c>
+      <c r="I198" s="2">
+        <v>0</v>
+      </c>
+      <c r="J198" s="2" t="s">
+        <v>180</v>
       </c>
     </row>
   </sheetData>
